--- a/emergencias.xlsx
+++ b/emergencias.xlsx
@@ -8,17 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whuatay\Documents\TDOCUMENTOS\2025\COE MIDIS\Aplicativo_web\6. COE_TABLERO_SEMANAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E9C503-EB42-4C00-BD83-88D09E0E6474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6662B442-341C-4309-A65E-15559D4D72D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta" sheetId="1" r:id="rId1"/>
     <sheet name="events" sheetId="2" r:id="rId2"/>
     <sheet name="impacto_programa" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">events!$A$1:$L$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">impacto_programa!$A$1:$H$30</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="4iWjnzOfOGPHSi/U+1150bvwc3li0ue47uJfuskbaKE="/>
     </ext>
@@ -27,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="326">
   <si>
     <t>fecha</t>
   </si>
@@ -335,9 +348,6 @@
     <t>Monzón</t>
   </si>
   <si>
-    <t>En monitoreo</t>
-  </si>
-  <si>
     <t>EV_2025_21</t>
   </si>
   <si>
@@ -860,9 +870,6 @@
     <t>Jaén</t>
   </si>
   <si>
-    <t>Activa</t>
-  </si>
-  <si>
     <t>CUNA MÁS: La UT informó que no se reportan daños a la salud de los usuarios</t>
   </si>
   <si>
@@ -875,9 +882,6 @@
     <t>Quillo</t>
   </si>
   <si>
-    <t>Cultivos perdidos</t>
-  </si>
-  <si>
     <t>CUNA MÁS: La UT realiza el seguimiento correspondiente</t>
   </si>
   <si>
@@ -962,9 +966,6 @@
     <t>CONTIGO</t>
   </si>
   <si>
-    <t>CUNA MAS</t>
-  </si>
-  <si>
     <t>PAIS</t>
   </si>
   <si>
@@ -977,7 +978,46 @@
     <t>Accidente transprote terrestre</t>
   </si>
   <si>
-    <t>PENSIÓN 65</t>
+    <t>EV_2025_93</t>
+  </si>
+  <si>
+    <t>Independencia</t>
+  </si>
+  <si>
+    <t>EV_2025_94</t>
+  </si>
+  <si>
+    <t>Espinar</t>
+  </si>
+  <si>
+    <t>Ocoruro</t>
+  </si>
+  <si>
+    <t>Accidente de transporte terrestre</t>
+  </si>
+  <si>
+    <t>EV_2025_95</t>
+  </si>
+  <si>
+    <t>Chincheros</t>
+  </si>
+  <si>
+    <t>Ocobamba</t>
+  </si>
+  <si>
+    <t>02 CIAI suspendidos por falta de acceso</t>
+  </si>
+  <si>
+    <t>FONCODES: La UT coodina con CUNA MÁS la evaluación de daños</t>
+  </si>
+  <si>
+    <t>FONCODES</t>
+  </si>
+  <si>
+    <t>CUNA MÁS</t>
+  </si>
+  <si>
+    <t>Sin novedad</t>
   </si>
 </sst>
 </file>
@@ -992,6 +1032,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1016,11 +1063,6 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1044,27 +1086,27 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2314,7 +2356,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L1000"/>
+  <dimension ref="A1:O1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -2327,7 +2369,8 @@
     <col min="8" max="8" width="18.140625" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
     <col min="10" max="10" width="25.28515625" customWidth="1"/>
-    <col min="11" max="26" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2391,7 +2434,7 @@
         <v>19</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>21</v>
@@ -3115,8 +3158,8 @@
       <c r="H21" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="7" t="s">
-        <v>102</v>
+      <c r="I21" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>22</v>
@@ -3130,7 +3173,7 @@
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B22" s="8">
         <v>45988</v>
@@ -3142,10 +3185,10 @@
         <v>56</v>
       </c>
       <c r="E22" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>105</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>58</v>
@@ -3168,7 +3211,7 @@
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B23" s="8">
         <v>45988</v>
@@ -3180,10 +3223,10 @@
         <v>56</v>
       </c>
       <c r="E23" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>108</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>58</v>
@@ -3206,7 +3249,7 @@
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B24" s="8">
         <v>45988</v>
@@ -3218,10 +3261,10 @@
         <v>56</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>58</v>
@@ -3244,7 +3287,7 @@
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B25" s="8">
         <v>45988</v>
@@ -3256,10 +3299,10 @@
         <v>56</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>58</v>
@@ -3282,7 +3325,7 @@
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B26" s="8">
         <v>45988</v>
@@ -3294,10 +3337,10 @@
         <v>56</v>
       </c>
       <c r="E26" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>113</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>114</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>58</v>
@@ -3320,7 +3363,7 @@
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B27" s="8">
         <v>45988</v>
@@ -3332,7 +3375,7 @@
         <v>56</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>56</v>
@@ -3358,7 +3401,7 @@
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B28" s="8">
         <v>45988</v>
@@ -3370,10 +3413,10 @@
         <v>56</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>58</v>
@@ -3382,7 +3425,7 @@
         <v>28</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J28" s="7" t="s">
         <v>22</v>
@@ -3396,7 +3439,7 @@
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B29" s="8">
         <v>45988</v>
@@ -3411,7 +3454,7 @@
         <v>74</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>58</v>
@@ -3434,7 +3477,7 @@
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" s="8">
         <v>45988</v>
@@ -3446,10 +3489,10 @@
         <v>56</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>58</v>
@@ -3472,7 +3515,7 @@
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B31" s="8">
         <v>45988</v>
@@ -3487,7 +3530,7 @@
         <v>61</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>58</v>
@@ -3510,7 +3553,7 @@
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B32" s="8">
         <v>45988</v>
@@ -3533,8 +3576,8 @@
       <c r="H32" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I32" s="7" t="s">
-        <v>102</v>
+      <c r="I32" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J32" s="7" t="s">
         <v>22</v>
@@ -3548,7 +3591,7 @@
     </row>
     <row r="33" spans="1:12" ht="15.75" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>45988</v>
@@ -3557,13 +3600,13 @@
         <v>45988</v>
       </c>
       <c r="D33" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="F33" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>58</v>
@@ -3571,8 +3614,8 @@
       <c r="H33" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I33" s="7" t="s">
-        <v>102</v>
+      <c r="I33" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>22</v>
@@ -3586,7 +3629,7 @@
     </row>
     <row r="34" spans="1:12" ht="15.75" customHeight="1">
       <c r="A34" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B34" s="8">
         <v>45988</v>
@@ -3595,13 +3638,13 @@
         <v>45988</v>
       </c>
       <c r="D34" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E34" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>132</v>
-      </c>
       <c r="F34" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>58</v>
@@ -3609,8 +3652,8 @@
       <c r="H34" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I34" s="7" t="s">
-        <v>102</v>
+      <c r="I34" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J34" s="7" t="s">
         <v>22</v>
@@ -3624,7 +3667,7 @@
     </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>45989</v>
@@ -3633,13 +3676,13 @@
         <v>45987</v>
       </c>
       <c r="D35" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="F35" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>51</v>
@@ -3647,8 +3690,8 @@
       <c r="H35" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I35" s="7" t="s">
-        <v>102</v>
+      <c r="I35" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J35" s="7" t="s">
         <v>22</v>
@@ -3662,7 +3705,7 @@
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B36" s="8">
         <v>45989</v>
@@ -3671,13 +3714,13 @@
         <v>45989</v>
       </c>
       <c r="D36" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="F36" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>140</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>58</v>
@@ -3685,8 +3728,8 @@
       <c r="H36" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I36" s="7" t="s">
-        <v>102</v>
+      <c r="I36" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J36" s="7" t="s">
         <v>22</v>
@@ -3700,7 +3743,7 @@
     </row>
     <row r="37" spans="1:12" ht="15.75" customHeight="1">
       <c r="A37" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="8">
         <v>45989</v>
@@ -3709,13 +3752,13 @@
         <v>45989</v>
       </c>
       <c r="D37" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="F37" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>58</v>
@@ -3723,8 +3766,8 @@
       <c r="H37" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I37" s="7" t="s">
-        <v>102</v>
+      <c r="I37" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J37" s="7" t="s">
         <v>22</v>
@@ -3738,7 +3781,7 @@
     </row>
     <row r="38" spans="1:12" ht="15.75" customHeight="1">
       <c r="A38" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="8">
         <v>45989</v>
@@ -3747,13 +3790,13 @@
         <v>45989</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E38" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>144</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>145</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>58</v>
@@ -3761,8 +3804,8 @@
       <c r="H38" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I38" s="7" t="s">
-        <v>102</v>
+      <c r="I38" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J38" s="7" t="s">
         <v>22</v>
@@ -3776,7 +3819,7 @@
     </row>
     <row r="39" spans="1:12" ht="15.75" customHeight="1">
       <c r="A39" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>45989</v>
@@ -3785,13 +3828,13 @@
         <v>45989</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>58</v>
@@ -3799,8 +3842,8 @@
       <c r="H39" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I39" s="7" t="s">
-        <v>102</v>
+      <c r="I39" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J39" s="7" t="s">
         <v>22</v>
@@ -3814,7 +3857,7 @@
     </row>
     <row r="40" spans="1:12" ht="15.75" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B40" s="8">
         <v>45989</v>
@@ -3823,13 +3866,13 @@
         <v>45989</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E40" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>150</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>58</v>
@@ -3837,8 +3880,8 @@
       <c r="H40" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I40" s="7" t="s">
-        <v>102</v>
+      <c r="I40" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J40" s="7" t="s">
         <v>22</v>
@@ -3852,7 +3895,7 @@
     </row>
     <row r="41" spans="1:12" ht="15.75" customHeight="1">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>45989</v>
@@ -3861,13 +3904,13 @@
         <v>45989</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E41" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F41" s="7" t="s">
         <v>152</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>153</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>58</v>
@@ -3875,8 +3918,8 @@
       <c r="H41" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I41" s="7" t="s">
-        <v>102</v>
+      <c r="I41" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J41" s="7" t="s">
         <v>22</v>
@@ -3890,7 +3933,7 @@
     </row>
     <row r="42" spans="1:12" ht="15.75" customHeight="1">
       <c r="A42" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B42" s="8">
         <v>45989</v>
@@ -3902,10 +3945,10 @@
         <v>79</v>
       </c>
       <c r="E42" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F42" s="7" t="s">
         <v>155</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>156</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>38</v>
@@ -3914,7 +3957,7 @@
         <v>28</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J42" s="7" t="s">
         <v>22</v>
@@ -3928,7 +3971,7 @@
     </row>
     <row r="43" spans="1:12" ht="15.75" customHeight="1">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>45989</v>
@@ -3940,10 +3983,10 @@
         <v>79</v>
       </c>
       <c r="E43" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F43" s="7" t="s">
         <v>159</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>160</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>58</v>
@@ -3952,7 +3995,7 @@
         <v>28</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J43" s="7" t="s">
         <v>22</v>
@@ -3966,7 +4009,7 @@
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1">
       <c r="A44" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B44" s="8">
         <v>45990</v>
@@ -3975,13 +4018,13 @@
         <v>45989</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E44" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F44" s="7" t="s">
         <v>163</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>164</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>58</v>
@@ -3990,7 +4033,7 @@
         <v>28</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J44" s="7" t="s">
         <v>22</v>
@@ -4004,7 +4047,7 @@
     </row>
     <row r="45" spans="1:12" ht="15.75" customHeight="1">
       <c r="A45" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>45990</v>
@@ -4016,13 +4059,13 @@
         <v>35</v>
       </c>
       <c r="E45" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G45" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>168</v>
       </c>
       <c r="H45" s="7" t="s">
         <v>28</v>
@@ -4042,7 +4085,7 @@
     </row>
     <row r="46" spans="1:12" ht="15.75" customHeight="1">
       <c r="A46" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B46" s="8">
         <v>45990</v>
@@ -4051,13 +4094,13 @@
         <v>45989</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E46" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F46" s="7" t="s">
         <v>170</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>171</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>81</v>
@@ -4080,7 +4123,7 @@
     </row>
     <row r="47" spans="1:12" ht="15.75" customHeight="1">
       <c r="A47" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>45990</v>
@@ -4089,13 +4132,13 @@
         <v>45989</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E47" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F47" s="7" t="s">
         <v>173</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>174</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>19</v>
@@ -4118,7 +4161,7 @@
     </row>
     <row r="48" spans="1:12" ht="15.75" customHeight="1">
       <c r="A48" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B48" s="8">
         <v>45990</v>
@@ -4130,10 +4173,10 @@
         <v>56</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>19</v>
@@ -4156,7 +4199,7 @@
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1">
       <c r="A49" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>45990</v>
@@ -4165,13 +4208,13 @@
         <v>45990</v>
       </c>
       <c r="D49" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>179</v>
-      </c>
       <c r="F49" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>94</v>
@@ -4194,7 +4237,7 @@
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1">
       <c r="A50" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B50" s="8">
         <v>45991</v>
@@ -4209,7 +4252,7 @@
         <v>97</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>81</v>
@@ -4232,7 +4275,7 @@
     </row>
     <row r="51" spans="1:12" ht="15.75" customHeight="1">
       <c r="A51" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B51" s="8">
         <v>45991</v>
@@ -4241,13 +4284,13 @@
         <v>45990</v>
       </c>
       <c r="D51" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="F51" s="7" t="s">
         <v>184</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>185</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>94</v>
@@ -4270,7 +4313,7 @@
     </row>
     <row r="52" spans="1:12" ht="15.75" customHeight="1">
       <c r="A52" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B52" s="8">
         <v>45991</v>
@@ -4282,19 +4325,19 @@
         <v>54</v>
       </c>
       <c r="E52" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F52" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="G52" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="G52" s="7" t="s">
+      <c r="H52" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I52" s="7" t="s">
         <v>189</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="7" t="s">
-        <v>190</v>
       </c>
       <c r="J52" s="7" t="s">
         <v>22</v>
@@ -4308,7 +4351,7 @@
     </row>
     <row r="53" spans="1:12" ht="15.75" customHeight="1">
       <c r="A53" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>45991</v>
@@ -4320,10 +4363,10 @@
         <v>32</v>
       </c>
       <c r="E53" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>192</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>193</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>94</v>
@@ -4346,7 +4389,7 @@
     </row>
     <row r="54" spans="1:12" ht="15.75" customHeight="1">
       <c r="A54" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B54" s="8">
         <v>45991</v>
@@ -4358,10 +4401,10 @@
         <v>32</v>
       </c>
       <c r="E54" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F54" s="7" t="s">
         <v>192</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>193</v>
       </c>
       <c r="G54" s="7" t="s">
         <v>94</v>
@@ -4384,7 +4427,7 @@
     </row>
     <row r="55" spans="1:12" ht="15.75" customHeight="1">
       <c r="A55" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>45992</v>
@@ -4396,10 +4439,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F55" s="7" t="s">
         <v>196</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>197</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>19</v>
@@ -4408,7 +4451,7 @@
         <v>28</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J55" s="7" t="s">
         <v>22</v>
@@ -4422,7 +4465,7 @@
     </row>
     <row r="56" spans="1:12" ht="15.75" customHeight="1">
       <c r="A56" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B56" s="8">
         <v>45992</v>
@@ -4434,19 +4477,19 @@
         <v>32</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F56" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G56" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="G56" s="7" t="s">
-        <v>201</v>
-      </c>
       <c r="H56" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I56" s="7" t="s">
-        <v>102</v>
+      <c r="I56" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J56" s="7" t="s">
         <v>22</v>
@@ -4460,7 +4503,7 @@
     </row>
     <row r="57" spans="1:12" ht="15.75" customHeight="1">
       <c r="A57" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>45992</v>
@@ -4475,7 +4518,7 @@
         <v>74</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>19</v>
@@ -4498,7 +4541,7 @@
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1">
       <c r="A58" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B58" s="8">
         <v>45992</v>
@@ -4510,10 +4553,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>51</v>
@@ -4536,7 +4579,7 @@
     </row>
     <row r="59" spans="1:12" ht="15.75" customHeight="1">
       <c r="A59" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B59" s="8">
         <v>45992</v>
@@ -4551,16 +4594,16 @@
         <v>18</v>
       </c>
       <c r="F59" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G59" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="G59" s="7" t="s">
-        <v>208</v>
-      </c>
       <c r="H59" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I59" s="7" t="s">
-        <v>102</v>
+      <c r="I59" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J59" s="7" t="s">
         <v>22</v>
@@ -4574,7 +4617,7 @@
     </row>
     <row r="60" spans="1:12" ht="15.75" customHeight="1">
       <c r="A60" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B60" s="8">
         <v>45993</v>
@@ -4586,10 +4629,10 @@
         <v>79</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>51</v>
@@ -4612,7 +4655,7 @@
     </row>
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
       <c r="A61" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B61" s="8">
         <v>45993</v>
@@ -4635,8 +4678,8 @@
       <c r="H61" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I61" s="7" t="s">
-        <v>102</v>
+      <c r="I61" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J61" s="7" t="s">
         <v>22</v>
@@ -4650,7 +4693,7 @@
     </row>
     <row r="62" spans="1:12" ht="15.75" customHeight="1">
       <c r="A62" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B62" s="8">
         <v>45993</v>
@@ -4662,10 +4705,10 @@
         <v>56</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>58</v>
@@ -4673,8 +4716,8 @@
       <c r="H62" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I62" s="7" t="s">
-        <v>102</v>
+      <c r="I62" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J62" s="7" t="s">
         <v>22</v>
@@ -4688,7 +4731,7 @@
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1">
       <c r="A63" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B63" s="8">
         <v>45993</v>
@@ -4700,10 +4743,10 @@
         <v>79</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>51</v>
@@ -4711,8 +4754,8 @@
       <c r="H63" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I63" s="7" t="s">
-        <v>102</v>
+      <c r="I63" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J63" s="7" t="s">
         <v>22</v>
@@ -4726,7 +4769,7 @@
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
       <c r="A64" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B64" s="8">
         <v>45993</v>
@@ -4738,10 +4781,10 @@
         <v>48</v>
       </c>
       <c r="E64" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="F64" s="7" t="s">
         <v>216</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>217</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>51</v>
@@ -4764,7 +4807,7 @@
     </row>
     <row r="65" spans="1:12" ht="15.75" customHeight="1">
       <c r="A65" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B65" s="8">
         <v>45993</v>
@@ -4779,7 +4822,7 @@
         <v>79</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>81</v>
@@ -4802,7 +4845,7 @@
     </row>
     <row r="66" spans="1:12" ht="15.75" customHeight="1">
       <c r="A66" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B66" s="8">
         <v>45994</v>
@@ -4814,10 +4857,10 @@
         <v>56</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>58</v>
@@ -4829,7 +4872,7 @@
         <v>52</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K66" s="7">
         <v>-5.7487069999999996</v>
@@ -4840,7 +4883,7 @@
     </row>
     <row r="67" spans="1:12" ht="15.75" customHeight="1">
       <c r="A67" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B67" s="8">
         <v>45994</v>
@@ -4849,13 +4892,13 @@
         <v>45992</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E67" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="F67" s="7" t="s">
         <v>224</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>225</v>
       </c>
       <c r="G67" s="7" t="s">
         <v>58</v>
@@ -4878,7 +4921,7 @@
     </row>
     <row r="68" spans="1:12" ht="15.75" customHeight="1">
       <c r="A68" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B68" s="8">
         <v>45994</v>
@@ -4887,13 +4930,13 @@
         <v>45993</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G68" s="7" t="s">
         <v>94</v>
@@ -4916,7 +4959,7 @@
     </row>
     <row r="69" spans="1:12" ht="15.75" customHeight="1">
       <c r="A69" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B69" s="8">
         <v>45995</v>
@@ -4928,13 +4971,13 @@
         <v>17</v>
       </c>
       <c r="E69" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F69" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="F69" s="7" t="s">
-        <v>230</v>
-      </c>
       <c r="G69" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H69" s="7" t="s">
         <v>28</v>
@@ -4954,7 +4997,7 @@
     </row>
     <row r="70" spans="1:12" ht="15.75" customHeight="1">
       <c r="A70" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B70" s="8">
         <v>45995</v>
@@ -4969,7 +5012,7 @@
         <v>25</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>51</v>
@@ -4992,7 +5035,7 @@
     </row>
     <row r="71" spans="1:12" ht="15.75" customHeight="1">
       <c r="A71" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B71" s="8">
         <v>45995</v>
@@ -5007,7 +5050,7 @@
         <v>79</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>81</v>
@@ -5030,7 +5073,7 @@
     </row>
     <row r="72" spans="1:12" ht="15.75" customHeight="1">
       <c r="A72" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B72" s="8">
         <v>45995</v>
@@ -5042,10 +5085,10 @@
         <v>79</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G72" s="7" t="s">
         <v>51</v>
@@ -5068,7 +5111,7 @@
     </row>
     <row r="73" spans="1:12" ht="15.75" customHeight="1">
       <c r="A73" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B73" s="8">
         <v>45995</v>
@@ -5080,10 +5123,10 @@
         <v>32</v>
       </c>
       <c r="E73" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F73" s="7" t="s">
         <v>238</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>239</v>
       </c>
       <c r="G73" s="7" t="s">
         <v>58</v>
@@ -5095,7 +5138,7 @@
         <v>52</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K73" s="7">
         <v>-11.083704000000001</v>
@@ -5106,7 +5149,7 @@
     </row>
     <row r="74" spans="1:12" ht="15.75" customHeight="1">
       <c r="A74" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B74" s="8">
         <v>45995</v>
@@ -5121,7 +5164,7 @@
         <v>41</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G74" s="7" t="s">
         <v>58</v>
@@ -5144,7 +5187,7 @@
     </row>
     <row r="75" spans="1:12" ht="15.75" customHeight="1">
       <c r="A75" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B75" s="8">
         <v>45996</v>
@@ -5156,10 +5199,10 @@
         <v>54</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G75" s="7" t="s">
         <v>94</v>
@@ -5168,10 +5211,10 @@
         <v>28</v>
       </c>
       <c r="I75" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="J75" s="7" t="s">
         <v>244</v>
-      </c>
-      <c r="J75" s="7" t="s">
-        <v>245</v>
       </c>
       <c r="K75" s="7">
         <v>-15.183208</v>
@@ -5182,7 +5225,7 @@
     </row>
     <row r="76" spans="1:12" ht="15.75" customHeight="1">
       <c r="A76" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B76" s="8">
         <v>45996</v>
@@ -5194,10 +5237,10 @@
         <v>32</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G76" s="7" t="s">
         <v>58</v>
@@ -5205,8 +5248,8 @@
       <c r="H76" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I76" s="7" t="s">
-        <v>102</v>
+      <c r="I76" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J76" s="7" t="s">
         <v>22</v>
@@ -5220,7 +5263,7 @@
     </row>
     <row r="77" spans="1:12" ht="15.75" customHeight="1">
       <c r="A77" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B77" s="8">
         <v>45996</v>
@@ -5238,13 +5281,13 @@
         <v>41</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H77" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I77" s="7" t="s">
-        <v>102</v>
+      <c r="I77" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J77" s="7" t="s">
         <v>22</v>
@@ -5258,7 +5301,7 @@
     </row>
     <row r="78" spans="1:12" ht="15.75" customHeight="1">
       <c r="A78" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B78" s="8">
         <v>45996</v>
@@ -5273,7 +5316,7 @@
         <v>41</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>38</v>
@@ -5282,10 +5325,10 @@
         <v>28</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J78" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K78" s="7">
         <v>-13.974194000000001</v>
@@ -5296,7 +5339,7 @@
     </row>
     <row r="79" spans="1:12" ht="15.75" customHeight="1">
       <c r="A79" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B79" s="8">
         <v>45997</v>
@@ -5308,22 +5351,22 @@
         <v>84</v>
       </c>
       <c r="E79" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F79" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>255</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>38</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K79" s="7">
         <v>-14.477164999999999</v>
@@ -5334,7 +5377,7 @@
     </row>
     <row r="80" spans="1:12" ht="15.75" customHeight="1">
       <c r="A80" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B80" s="8">
         <v>45998</v>
@@ -5346,22 +5389,22 @@
         <v>68</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G80" s="7" t="s">
         <v>38</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I80" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K80" s="7">
         <v>-11.475307000000001</v>
@@ -5370,9 +5413,9 @@
         <v>-76.582296999999997</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="15.75" customHeight="1">
+    <row r="81" spans="1:15" ht="15.75" customHeight="1">
       <c r="A81" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B81" s="8">
         <v>45998</v>
@@ -5384,22 +5427,22 @@
         <v>17</v>
       </c>
       <c r="E81" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="F81" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="F81" s="7" t="s">
+      <c r="G81" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="G81" s="7" t="s">
+      <c r="H81" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I81" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="H81" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I81" s="7" t="s">
+      <c r="J81" s="7" t="s">
         <v>263</v>
-      </c>
-      <c r="J81" s="7" t="s">
-        <v>264</v>
       </c>
       <c r="K81" s="7">
         <v>-9.7938259999999993</v>
@@ -5408,9 +5451,9 @@
         <v>-76.766863000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15.75" customHeight="1">
+    <row r="82" spans="1:15" ht="15.75" customHeight="1">
       <c r="A82" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B82" s="8">
         <v>45999</v>
@@ -5422,22 +5465,22 @@
         <v>32</v>
       </c>
       <c r="E82" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F82" s="7" t="s">
         <v>192</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>193</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>58</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I82" s="7" t="s">
-        <v>102</v>
+        <v>28</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K82" s="7">
         <v>-7.965052</v>
@@ -5446,9 +5489,9 @@
         <v>-74.160190999999998</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15.75" customHeight="1">
+    <row r="83" spans="1:15" ht="15.75" customHeight="1">
       <c r="A83" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B83" s="8">
         <v>45999</v>
@@ -5460,22 +5503,22 @@
         <v>32</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G83" s="7" t="s">
         <v>58</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I83" s="7" t="s">
-        <v>102</v>
+        <v>28</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K83" s="7">
         <v>-8.5384309999999992</v>
@@ -5484,9 +5527,9 @@
         <v>-74.509163999999998</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="15.75" customHeight="1">
+    <row r="84" spans="1:15" ht="15.75" customHeight="1">
       <c r="A84" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B84" s="8">
         <v>46001</v>
@@ -5498,22 +5541,22 @@
         <v>68</v>
       </c>
       <c r="E84" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="F84" s="7" t="s">
         <v>268</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>269</v>
       </c>
       <c r="G84" s="7" t="s">
         <v>38</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I84" s="7" t="s">
-        <v>102</v>
+        <v>28</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K84" s="7">
         <v>-12.887559</v>
@@ -5522,9 +5565,9 @@
         <v>-75.770426999999998</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="15.75" customHeight="1">
+    <row r="85" spans="1:15" ht="15.75" customHeight="1">
       <c r="A85" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B85" s="8">
         <v>46001</v>
@@ -5533,25 +5576,25 @@
         <v>46000</v>
       </c>
       <c r="D85" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E85" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E85" s="7" t="s">
-        <v>128</v>
-      </c>
       <c r="F85" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="G85" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="G85" s="7" t="s">
+      <c r="H85" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I85" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="H85" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I85" s="7" t="s">
-        <v>274</v>
-      </c>
       <c r="J85" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K85" s="7">
         <v>-6.5176100000000003</v>
@@ -5560,9 +5603,9 @@
         <v>-78.495239999999995</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="15.75" customHeight="1">
+    <row r="86" spans="1:15" ht="15.75" customHeight="1">
       <c r="A86" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B86" s="8">
         <v>46001</v>
@@ -5571,25 +5614,25 @@
         <v>46001</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G86" s="7" t="s">
         <v>58</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="I86" s="7" t="s">
-        <v>102</v>
+        <v>28</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K86" s="7">
         <v>-5.7701840000000004</v>
@@ -5598,9 +5641,9 @@
         <v>-78.852553</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="15.75" customHeight="1">
+    <row r="87" spans="1:15" ht="15.75" customHeight="1">
       <c r="A87" s="7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B87" s="8">
         <v>46001</v>
@@ -5608,26 +5651,26 @@
       <c r="C87" s="8">
         <v>45998</v>
       </c>
-      <c r="D87" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E87" s="7" t="s">
+      <c r="D87" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="J87" s="8" t="s">
         <v>280</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I87" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>283</v>
       </c>
       <c r="K87" s="7">
         <v>-6.5176100000000003</v>
@@ -5635,10 +5678,13 @@
       <c r="L87" s="7">
         <v>-78.495239999999995</v>
       </c>
-    </row>
-    <row r="88" spans="1:12" ht="15.75" customHeight="1">
+      <c r="M87" s="8"/>
+      <c r="N87" s="8"/>
+      <c r="O87" s="8"/>
+    </row>
+    <row r="88" spans="1:15" ht="15.75" customHeight="1">
       <c r="A88" s="7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B88" s="8">
         <v>46001</v>
@@ -5646,26 +5692,26 @@
       <c r="C88" s="8">
         <v>45999</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D88" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E88" s="7" t="s">
+      <c r="E88" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F88" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="G88" s="7" t="s">
+      <c r="F88" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="G88" s="8" t="s">
         <v>19</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I88" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="J88" s="7" t="s">
-        <v>264</v>
+        <v>28</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="J88" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="K88" s="7">
         <v>-8.8249340000000007</v>
@@ -5673,37 +5719,40 @@
       <c r="L88" s="7">
         <v>-75.047983000000002</v>
       </c>
-    </row>
-    <row r="89" spans="1:12" ht="15.75" customHeight="1">
+      <c r="M88" s="8"/>
+      <c r="N88" s="8"/>
+      <c r="O88" s="8"/>
+    </row>
+    <row r="89" spans="1:15" ht="15.75" customHeight="1">
       <c r="A89" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B89" s="8">
         <v>46002</v>
       </c>
-      <c r="C89" s="7">
+      <c r="C89" s="8">
         <v>46000</v>
       </c>
-      <c r="D89" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E89" s="7" t="s">
+      <c r="D89" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I89" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="F89" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="H89" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I89" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="J89" s="7" t="s">
-        <v>264</v>
+      <c r="J89" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="K89" s="7">
         <v>-9.4665780000000002</v>
@@ -5711,156 +5760,290 @@
       <c r="L89" s="7">
         <v>-76.982342000000003</v>
       </c>
-    </row>
-    <row r="90" spans="1:12" ht="15.75" customHeight="1">
+      <c r="M89" s="8"/>
+      <c r="N89" s="8"/>
+      <c r="O89" s="8"/>
+    </row>
+    <row r="90" spans="1:15" ht="15.75" customHeight="1">
       <c r="A90" t="s">
+        <v>289</v>
+      </c>
+      <c r="B90" s="8">
+        <v>46002</v>
+      </c>
+      <c r="C90" s="8">
+        <v>46001</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I90" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="B90">
+      <c r="J90" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="K90" s="7">
+        <v>-5.8458800000000002</v>
+      </c>
+      <c r="L90" s="7">
+        <v>-76.161581999999996</v>
+      </c>
+      <c r="M90" s="8"/>
+      <c r="N90" s="8"/>
+      <c r="O90" s="8"/>
+    </row>
+    <row r="91" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A91" t="s">
+        <v>293</v>
+      </c>
+      <c r="B91" s="8">
         <v>46002</v>
       </c>
-      <c r="C90">
+      <c r="C91" s="8">
+        <v>46000</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="J91" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="K91" s="7">
+        <v>-11.530968</v>
+      </c>
+      <c r="L91" s="7">
+        <v>-73.814445000000006</v>
+      </c>
+      <c r="M91" s="8"/>
+      <c r="N91" s="8"/>
+      <c r="O91" s="8"/>
+    </row>
+    <row r="92" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A92" t="s">
+        <v>298</v>
+      </c>
+      <c r="B92" s="8">
+        <v>46002</v>
+      </c>
+      <c r="C92" s="8">
         <v>46001</v>
       </c>
-      <c r="D90" t="s">
-        <v>48</v>
-      </c>
-      <c r="E90" t="s">
-        <v>293</v>
-      </c>
-      <c r="F90" t="s">
-        <v>294</v>
-      </c>
-      <c r="G90" t="s">
+      <c r="D92" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="J92" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="K92" s="7">
+        <v>-9.8965709999999998</v>
+      </c>
+      <c r="L92" s="7">
+        <v>-76.296696999999995</v>
+      </c>
+      <c r="M92" s="8"/>
+      <c r="N92" s="8"/>
+      <c r="O92" s="8"/>
+    </row>
+    <row r="93" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A93" t="s">
+        <v>309</v>
+      </c>
+      <c r="B93" s="8">
+        <v>46003</v>
+      </c>
+      <c r="C93" s="8">
+        <v>46002</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="K93" s="7">
+        <v>-10.792036</v>
+      </c>
+      <c r="L93" s="7">
+        <v>-76.060196000000005</v>
+      </c>
+      <c r="M93" s="8"/>
+      <c r="N93" s="8"/>
+      <c r="O93" s="8"/>
+    </row>
+    <row r="94" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A94" t="s">
+        <v>312</v>
+      </c>
+      <c r="B94" s="8">
+        <v>46003</v>
+      </c>
+      <c r="C94" s="8">
+        <v>46003</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="G94" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H94" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="J94" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="K94" s="7">
+        <v>-11.987477</v>
+      </c>
+      <c r="L94" s="7">
+        <v>-77.046008</v>
+      </c>
+      <c r="M94" s="8"/>
+      <c r="N94" s="8"/>
+      <c r="O94" s="8"/>
+    </row>
+    <row r="95" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A95" t="s">
+        <v>314</v>
+      </c>
+      <c r="B95" s="8">
+        <v>46003</v>
+      </c>
+      <c r="C95" s="8">
+        <v>46002</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="J95" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="K95" s="7">
+        <v>-15.087897</v>
+      </c>
+      <c r="L95" s="7">
+        <v>-71.138992999999999</v>
+      </c>
+      <c r="M95" s="8"/>
+      <c r="N95" s="8"/>
+      <c r="O95" s="8"/>
+    </row>
+    <row r="96" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A96" t="s">
+        <v>318</v>
+      </c>
+      <c r="B96" s="8">
+        <v>46003</v>
+      </c>
+      <c r="C96" s="8">
+        <v>46003</v>
+      </c>
+      <c r="D96" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" t="s">
+        <v>319</v>
+      </c>
+      <c r="F96" t="s">
+        <v>320</v>
+      </c>
+      <c r="G96" t="s">
+        <v>58</v>
+      </c>
+      <c r="H96" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I90" t="s">
-        <v>295</v>
-      </c>
-      <c r="J90" t="s">
-        <v>264</v>
-      </c>
-      <c r="K90">
-        <v>-5.8458800000000002</v>
-      </c>
-      <c r="L90">
-        <v>-76.161581999999996</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A91" t="s">
-        <v>296</v>
-      </c>
-      <c r="B91">
-        <v>46002</v>
-      </c>
-      <c r="C91">
-        <v>46000</v>
-      </c>
-      <c r="D91" t="s">
-        <v>297</v>
-      </c>
-      <c r="E91" t="s">
-        <v>298</v>
-      </c>
-      <c r="F91" t="s">
-        <v>299</v>
-      </c>
-      <c r="G91" t="s">
-        <v>58</v>
-      </c>
-      <c r="H91" t="s">
-        <v>20</v>
-      </c>
-      <c r="I91" t="s">
-        <v>300</v>
-      </c>
-      <c r="J91" t="s">
-        <v>264</v>
-      </c>
-      <c r="K91">
-        <v>-11.530968</v>
-      </c>
-      <c r="L91">
-        <v>-73.814445000000006</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A92" t="s">
-        <v>301</v>
-      </c>
-      <c r="B92">
-        <v>46002</v>
-      </c>
-      <c r="C92">
-        <v>46001</v>
-      </c>
-      <c r="D92" t="s">
-        <v>17</v>
-      </c>
-      <c r="G92" t="s">
-        <v>302</v>
-      </c>
-      <c r="H92" t="s">
-        <v>20</v>
-      </c>
-      <c r="I92" t="s">
-        <v>102</v>
-      </c>
-      <c r="J92" t="s">
-        <v>264</v>
-      </c>
-      <c r="K92">
-        <v>-9.8965709999999998</v>
-      </c>
-      <c r="L92">
-        <v>-76.296696999999995</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A93" t="s">
-        <v>313</v>
-      </c>
-      <c r="B93">
-        <v>46003</v>
-      </c>
-      <c r="C93">
-        <v>46002</v>
-      </c>
-      <c r="D93" t="s">
-        <v>44</v>
-      </c>
-      <c r="E93" t="s">
-        <v>44</v>
-      </c>
-      <c r="F93" t="s">
-        <v>314</v>
-      </c>
-      <c r="G93" t="s">
-        <v>315</v>
-      </c>
-      <c r="H93" t="s">
-        <v>20</v>
-      </c>
-      <c r="I93" t="s">
-        <v>102</v>
-      </c>
-      <c r="J93" t="s">
-        <v>264</v>
-      </c>
-      <c r="K93">
-        <v>-10.792036</v>
-      </c>
-      <c r="L93">
-        <v>-76.060196000000005</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="95" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="96" spans="1:12" ht="15.75" customHeight="1"/>
+      <c r="I96" t="s">
+        <v>321</v>
+      </c>
+      <c r="J96" t="s">
+        <v>322</v>
+      </c>
+      <c r="K96">
+        <v>-13.506117</v>
+      </c>
+      <c r="L96">
+        <v>-73.519602000000006</v>
+      </c>
+    </row>
     <row r="97" ht="15.75" customHeight="1"/>
     <row r="98" ht="15.75" customHeight="1"/>
     <row r="99" ht="15.75" customHeight="1"/>
@@ -6766,6 +6949,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <autoFilter ref="A1:L96" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -6773,7 +6957,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:H1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
@@ -6783,346 +6967,530 @@
     <col min="7" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E1" t="s">
         <v>303</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="F1" t="s">
         <v>304</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
         <v>305</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>45981</v>
+      </c>
+      <c r="H2">
+        <v>45981</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
         <v>306</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>45981</v>
+      </c>
+      <c r="H3">
+        <v>45981</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>305</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>45986</v>
+      </c>
+      <c r="H4">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>45986</v>
+      </c>
+      <c r="H5">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" t="s">
+        <v>305</v>
+      </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>45986</v>
+      </c>
+      <c r="H6">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>45986</v>
+      </c>
+      <c r="H7">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" t="s">
+        <v>324</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>28</v>
+      </c>
+      <c r="G8">
+        <v>45988</v>
+      </c>
+      <c r="H8">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" t="s">
+        <v>306</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>45989</v>
+      </c>
+      <c r="H9">
+        <v>45989</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>45991</v>
+      </c>
+      <c r="H10">
+        <v>45991</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" t="s">
+        <v>305</v>
+      </c>
+      <c r="C11">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>45991</v>
+      </c>
+      <c r="H11">
+        <v>45991</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" t="s">
+        <v>324</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12">
+        <v>45992</v>
+      </c>
+      <c r="H12">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" t="s">
+        <v>306</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>45992</v>
+      </c>
+      <c r="H13">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" t="s">
         <v>308</v>
       </c>
-      <c r="C2" s="7">
+      <c r="F14">
+        <v>12</v>
+      </c>
+      <c r="G14">
+        <v>45992</v>
+      </c>
+      <c r="H14">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>217</v>
+      </c>
+      <c r="B15" t="s">
+        <v>305</v>
+      </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
+      <c r="G15">
+        <v>45987</v>
+      </c>
+      <c r="H15">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" t="s">
+        <v>323</v>
+      </c>
+      <c r="C16">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>46002</v>
+      </c>
+      <c r="H16">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>219</v>
+      </c>
+      <c r="B17" t="s">
+        <v>306</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>45993</v>
+      </c>
+      <c r="H17">
+        <v>45993</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>219</v>
+      </c>
+      <c r="B18" t="s">
+        <v>307</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>45993</v>
+      </c>
+      <c r="H18">
+        <v>45993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" t="s">
+        <v>306</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>45987</v>
+      </c>
+      <c r="H19">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C3" s="7">
+      <c r="G20">
+        <v>45987</v>
+      </c>
+      <c r="H20">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B21" t="s">
+        <v>305</v>
+      </c>
+      <c r="C21">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="G21">
+        <v>45989</v>
+      </c>
+      <c r="H21">
+        <v>45989</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" t="s">
+        <v>306</v>
+      </c>
+      <c r="C22">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C5" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C6" s="7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C8" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="G22">
+        <v>45987</v>
+      </c>
+      <c r="H22">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A23" t="s">
+        <v>227</v>
+      </c>
+      <c r="B23" t="s">
+        <v>306</v>
+      </c>
+      <c r="C23">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="G23">
+        <v>45994</v>
+      </c>
+      <c r="H23">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B24" t="s">
+        <v>324</v>
+      </c>
+      <c r="D24">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="G24">
+        <v>45994</v>
+      </c>
+      <c r="H24">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A25" t="s">
+        <v>240</v>
+      </c>
+      <c r="B25" t="s">
+        <v>324</v>
+      </c>
+      <c r="D25">
         <v>1</v>
       </c>
-      <c r="E11" s="7">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="G25">
+        <v>45995</v>
+      </c>
+      <c r="H25">
+        <v>45995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A26" t="s">
+        <v>222</v>
+      </c>
+      <c r="B26" t="s">
+        <v>324</v>
+      </c>
+      <c r="C26">
+        <v>13</v>
+      </c>
+      <c r="G26">
+        <v>45994</v>
+      </c>
+      <c r="H26">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A27" t="s">
+        <v>245</v>
+      </c>
+      <c r="B27" t="s">
+        <v>324</v>
+      </c>
+      <c r="C27">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="C13" s="7">
+      <c r="G27">
+        <v>45996</v>
+      </c>
+      <c r="H27">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A28" t="s">
+        <v>277</v>
+      </c>
+      <c r="B28" t="s">
+        <v>324</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>46001</v>
+      </c>
+      <c r="H28">
+        <v>45998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A29" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" t="s">
+        <v>307</v>
+      </c>
+      <c r="C29">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C14" s="7">
+      <c r="G29">
+        <v>46002</v>
+      </c>
+      <c r="H29">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A30" t="s">
+        <v>289</v>
+      </c>
+      <c r="B30" t="s">
+        <v>306</v>
+      </c>
+      <c r="C30">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C15" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="F16" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="F17" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="F18" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C19" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C20" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A21" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C21" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A22" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="C22" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A23" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="C23" s="7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A24" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C24" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A25" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="D25" s="7">
-        <v>1</v>
-      </c>
-      <c r="E25" s="9">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A26" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="D26" s="7">
-        <v>1</v>
-      </c>
-      <c r="E26" s="9">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A27" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="C27" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A28" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="C28" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A29" t="s">
-        <v>292</v>
-      </c>
-      <c r="B29" t="s">
-        <v>316</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1"/>
+      <c r="G30">
+        <v>46002</v>
+      </c>
+      <c r="H30">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -8092,6 +8460,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <autoFilter ref="A1:H30" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/emergencias.xlsx
+++ b/emergencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whuatay\Documents\TDOCUMENTOS\2025\COE MIDIS\Aplicativo_web\6. COE_TABLERO_SEMANAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6662B442-341C-4309-A65E-15559D4D72D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E93F237-78B0-403C-935C-701915073879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="impacto_programa" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">events!$A$1:$L$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">events!$A$2:$L$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">impacto_programa!$A$1:$H$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6949,7 +6949,6 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:L96" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -7097,44 +7096,41 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>324</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>28</v>
+        <v>306</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
       </c>
       <c r="G8">
-        <v>45988</v>
+        <v>45987</v>
       </c>
       <c r="H8">
-        <v>45988</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s">
-        <v>306</v>
-      </c>
-      <c r="F9">
+        <v>307</v>
+      </c>
+      <c r="C9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>45989</v>
+        <v>45987</v>
       </c>
       <c r="H9">
-        <v>45989</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>194</v>
+        <v>99</v>
       </c>
       <c r="B10" t="s">
         <v>306</v>
@@ -7143,174 +7139,177 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>45991</v>
+        <v>45987</v>
       </c>
       <c r="H10">
-        <v>45991</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>194</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>305</v>
-      </c>
-      <c r="C11">
-        <v>12</v>
+        <v>324</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>28</v>
       </c>
       <c r="G11">
-        <v>45991</v>
+        <v>45988</v>
       </c>
       <c r="H11">
-        <v>45991</v>
+        <v>45988</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>45992</v>
+        <v>45989</v>
       </c>
       <c r="H12">
-        <v>45992</v>
+        <v>45989</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s">
-        <v>306</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
+        <v>307</v>
+      </c>
+      <c r="C13">
+        <v>30</v>
       </c>
       <c r="G13">
-        <v>45992</v>
+        <v>46002</v>
       </c>
       <c r="H13">
-        <v>45992</v>
+        <v>45986</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B14" t="s">
-        <v>308</v>
-      </c>
-      <c r="F14">
-        <v>12</v>
+        <v>306</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>45992</v>
+        <v>45991</v>
       </c>
       <c r="H14">
-        <v>45992</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s">
         <v>305</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G15">
-        <v>45987</v>
+        <v>45991</v>
       </c>
       <c r="H15">
-        <v>45987</v>
+        <v>45991</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s">
-        <v>323</v>
-      </c>
-      <c r="C16">
-        <v>11</v>
+        <v>324</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>46002</v>
+        <v>45992</v>
       </c>
       <c r="H16">
-        <v>45987</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
         <v>306</v>
       </c>
-      <c r="C17">
-        <v>2</v>
+      <c r="F17">
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>45993</v>
+        <v>45992</v>
       </c>
       <c r="H17">
-        <v>45993</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>307</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
+        <v>308</v>
+      </c>
+      <c r="F18">
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>45993</v>
+        <v>45992</v>
       </c>
       <c r="H18">
-        <v>45993</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="H19">
-        <v>45987</v>
+        <v>45989</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="B20" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G20">
         <v>45987</v>
@@ -7321,64 +7320,64 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G21">
-        <v>45989</v>
+        <v>46002</v>
       </c>
       <c r="H21">
-        <v>45989</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s">
         <v>306</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>45987</v>
+        <v>45993</v>
       </c>
       <c r="H22">
-        <v>45987</v>
+        <v>45993</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>45994</v>
+        <v>45993</v>
       </c>
       <c r="H23">
-        <v>45994</v>
+        <v>45993</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s">
         <v>324</v>
       </c>
-      <c r="D24">
-        <v>1</v>
+      <c r="C24">
+        <v>13</v>
       </c>
       <c r="G24">
         <v>45994</v>
@@ -7389,30 +7388,30 @@
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s">
-        <v>324</v>
-      </c>
-      <c r="D25">
+        <v>306</v>
+      </c>
+      <c r="C25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>45995</v>
+        <v>45994</v>
       </c>
       <c r="H25">
-        <v>45995</v>
+        <v>45994</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s">
         <v>324</v>
       </c>
-      <c r="C26">
-        <v>13</v>
+      <c r="D26">
+        <v>1</v>
       </c>
       <c r="G26">
         <v>45994</v>
@@ -7423,24 +7422,24 @@
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s">
         <v>324</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>1</v>
       </c>
       <c r="G27">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="H27">
-        <v>45996</v>
+        <v>45995</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s">
         <v>324</v>
@@ -7449,27 +7448,27 @@
         <v>1</v>
       </c>
       <c r="G28">
-        <v>46001</v>
+        <v>45996</v>
       </c>
       <c r="H28">
-        <v>45998</v>
+        <v>45996</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" t="s">
-        <v>157</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="C29">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="H29">
-        <v>45986</v>
+        <v>45998</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
@@ -8460,7 +8459,9 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:H30" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H30">
+    <sortCondition ref="A2:A30"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/emergencias.xlsx
+++ b/emergencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whuatay\Documents\TDOCUMENTOS\2025\COE MIDIS\Aplicativo_web\6. COE_TABLERO_SEMANAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E93F237-78B0-403C-935C-701915073879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CFB663-DE8E-4938-8882-7CEB3CED522C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="338">
   <si>
     <t>fecha</t>
   </si>
@@ -1018,6 +1018,42 @@
   </si>
   <si>
     <t>Sin novedad</t>
+  </si>
+  <si>
+    <t>EV_2025_96</t>
+  </si>
+  <si>
+    <t>Belen</t>
+  </si>
+  <si>
+    <t>Personas damnificadas y viviendas destruidas</t>
+  </si>
+  <si>
+    <t>EV_2025_97</t>
+  </si>
+  <si>
+    <t>Echerate</t>
+  </si>
+  <si>
+    <t>Activa</t>
+  </si>
+  <si>
+    <t>El tránsito (tramo Echarate – Santa Ana) fue restablecido</t>
+  </si>
+  <si>
+    <t>EV_2025_98</t>
+  </si>
+  <si>
+    <t>Callao</t>
+  </si>
+  <si>
+    <t>Ventanilla</t>
+  </si>
+  <si>
+    <t>1 IE afectada (muro perimétrico)</t>
+  </si>
+  <si>
+    <t>DRE-UGEL del Callao: realizan acciones de respuesta competentes a su sector</t>
   </si>
 </sst>
 </file>
@@ -6044,22 +6080,133 @@
         <v>-73.519602000000006</v>
       </c>
     </row>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="97" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A97" t="s">
+        <v>326</v>
+      </c>
+      <c r="B97" s="8">
+        <v>46006</v>
+      </c>
+      <c r="C97" s="8">
+        <v>46005</v>
+      </c>
+      <c r="D97" t="s">
+        <v>48</v>
+      </c>
+      <c r="E97" t="s">
+        <v>49</v>
+      </c>
+      <c r="F97" t="s">
+        <v>327</v>
+      </c>
+      <c r="G97" t="s">
+        <v>94</v>
+      </c>
+      <c r="H97" t="s">
+        <v>20</v>
+      </c>
+      <c r="I97" t="s">
+        <v>328</v>
+      </c>
+      <c r="J97" t="s">
+        <v>263</v>
+      </c>
+      <c r="K97">
+        <v>-3.811598</v>
+      </c>
+      <c r="L97">
+        <v>-73.211978000000002</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A98" t="s">
+        <v>329</v>
+      </c>
+      <c r="B98" s="8">
+        <v>46006</v>
+      </c>
+      <c r="C98" s="8">
+        <v>46006</v>
+      </c>
+      <c r="D98" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98" t="s">
+        <v>330</v>
+      </c>
+      <c r="G98" t="s">
+        <v>167</v>
+      </c>
+      <c r="H98" t="s">
+        <v>331</v>
+      </c>
+      <c r="I98" t="s">
+        <v>251</v>
+      </c>
+      <c r="J98" t="s">
+        <v>332</v>
+      </c>
+      <c r="K98">
+        <v>-12.355022</v>
+      </c>
+      <c r="L98">
+        <v>-72.832802999999998</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A99" t="s">
+        <v>333</v>
+      </c>
+      <c r="B99" s="8">
+        <v>46006</v>
+      </c>
+      <c r="C99" s="8">
+        <v>46004</v>
+      </c>
+      <c r="D99" t="s">
+        <v>334</v>
+      </c>
+      <c r="E99" t="s">
+        <v>334</v>
+      </c>
+      <c r="F99" t="s">
+        <v>335</v>
+      </c>
+      <c r="G99" t="s">
+        <v>248</v>
+      </c>
+      <c r="H99" t="s">
+        <v>20</v>
+      </c>
+      <c r="I99" t="s">
+        <v>336</v>
+      </c>
+      <c r="J99" t="s">
+        <v>337</v>
+      </c>
+      <c r="K99">
+        <v>-12.355022</v>
+      </c>
+      <c r="L99">
+        <v>-72.832802999999998</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="101" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="102" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="103" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="104" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="105" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="106" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="107" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="108" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="109" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="110" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="111" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="112" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="113" ht="15.75" customHeight="1"/>
     <row r="114" ht="15.75" customHeight="1"/>
     <row r="115" ht="15.75" customHeight="1"/>

--- a/emergencias.xlsx
+++ b/emergencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whuatay\Documents\TDOCUMENTOS\2025\COE MIDIS\Aplicativo_web\6. COE_TABLERO_SEMANAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CFB663-DE8E-4938-8882-7CEB3CED522C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F6ABB8-BA0C-4062-B37F-801185739776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="364">
   <si>
     <t>fecha</t>
   </si>
@@ -1054,6 +1054,84 @@
   </si>
   <si>
     <t>DRE-UGEL del Callao: realizan acciones de respuesta competentes a su sector</t>
+  </si>
+  <si>
+    <t>EV_2025_99</t>
+  </si>
+  <si>
+    <t>EV_2025_100</t>
+  </si>
+  <si>
+    <t>Paucar del Sara Sara</t>
+  </si>
+  <si>
+    <t>Pararca</t>
+  </si>
+  <si>
+    <t>Incendio Forestal</t>
+  </si>
+  <si>
+    <t>Cobertura natural destruida</t>
+  </si>
+  <si>
+    <t>EV_2025_101</t>
+  </si>
+  <si>
+    <t>Yanacancha</t>
+  </si>
+  <si>
+    <t>99 personas afectadas 16 viviendas afectadas</t>
+  </si>
+  <si>
+    <t>EV_2025_102</t>
+  </si>
+  <si>
+    <t>Arequipa</t>
+  </si>
+  <si>
+    <t>Cerro colorado</t>
+  </si>
+  <si>
+    <t>Enfermedades virales</t>
+  </si>
+  <si>
+    <t>01 CIAI suspendido</t>
+  </si>
+  <si>
+    <t>EV_2025_103</t>
+  </si>
+  <si>
+    <t>Acobamba</t>
+  </si>
+  <si>
+    <t>Marcas</t>
+  </si>
+  <si>
+    <t>EV_2025_104</t>
+  </si>
+  <si>
+    <t>La Victoria</t>
+  </si>
+  <si>
+    <t>Incendio urbano</t>
+  </si>
+  <si>
+    <t>EV_2025_105</t>
+  </si>
+  <si>
+    <t>Requena</t>
+  </si>
+  <si>
+    <t>Saquena</t>
+  </si>
+  <si>
+    <t>Erosión</t>
+  </si>
+  <si>
+    <t>CUNA MAS</t>
+  </si>
+  <si>
+    <t>PENSIÓN 65</t>
   </si>
 </sst>
 </file>
@@ -2395,7 +2473,7 @@
   <dimension ref="A1:O1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
     <col min="2" max="2" width="15.85546875" customWidth="1"/>
     <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" customWidth="1"/>
@@ -6194,13 +6272,272 @@
         <v>-72.832802999999998</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="101" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="102" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="103" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="104" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="105" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="106" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="100" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A100" t="s">
+        <v>338</v>
+      </c>
+      <c r="B100" s="8">
+        <v>46006</v>
+      </c>
+      <c r="C100" s="8">
+        <v>46004</v>
+      </c>
+      <c r="D100" t="s">
+        <v>334</v>
+      </c>
+      <c r="E100" t="s">
+        <v>334</v>
+      </c>
+      <c r="F100" t="s">
+        <v>335</v>
+      </c>
+      <c r="G100" t="s">
+        <v>248</v>
+      </c>
+      <c r="H100" t="s">
+        <v>20</v>
+      </c>
+      <c r="I100" t="s">
+        <v>336</v>
+      </c>
+      <c r="J100" t="s">
+        <v>337</v>
+      </c>
+      <c r="K100">
+        <v>-11.879155000000001</v>
+      </c>
+      <c r="L100">
+        <v>-77.130874000000006</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A101" t="s">
+        <v>339</v>
+      </c>
+      <c r="B101" s="8">
+        <v>46006</v>
+      </c>
+      <c r="C101" s="8">
+        <v>46006</v>
+      </c>
+      <c r="D101" t="s">
+        <v>84</v>
+      </c>
+      <c r="E101" t="s">
+        <v>340</v>
+      </c>
+      <c r="F101" t="s">
+        <v>341</v>
+      </c>
+      <c r="G101" t="s">
+        <v>342</v>
+      </c>
+      <c r="H101" t="s">
+        <v>331</v>
+      </c>
+      <c r="I101" t="s">
+        <v>343</v>
+      </c>
+      <c r="J101" t="s">
+        <v>263</v>
+      </c>
+      <c r="K101">
+        <v>-15.205722</v>
+      </c>
+      <c r="L101">
+        <v>-73.452313000000004</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A102" t="s">
+        <v>344</v>
+      </c>
+      <c r="B102" s="8">
+        <v>46007</v>
+      </c>
+      <c r="C102" s="8">
+        <v>46006</v>
+      </c>
+      <c r="D102" t="s">
+        <v>44</v>
+      </c>
+      <c r="E102" t="s">
+        <v>44</v>
+      </c>
+      <c r="F102" t="s">
+        <v>345</v>
+      </c>
+      <c r="G102" t="s">
+        <v>51</v>
+      </c>
+      <c r="H102" t="s">
+        <v>331</v>
+      </c>
+      <c r="I102" t="s">
+        <v>346</v>
+      </c>
+      <c r="J102" t="s">
+        <v>263</v>
+      </c>
+      <c r="K102">
+        <v>-10.643432000000001</v>
+      </c>
+      <c r="L102">
+        <v>-76.194277999999997</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A103" t="s">
+        <v>347</v>
+      </c>
+      <c r="B103" s="8">
+        <v>46007</v>
+      </c>
+      <c r="C103" s="8">
+        <v>46007</v>
+      </c>
+      <c r="D103" t="s">
+        <v>348</v>
+      </c>
+      <c r="E103" t="s">
+        <v>348</v>
+      </c>
+      <c r="F103" t="s">
+        <v>349</v>
+      </c>
+      <c r="G103" t="s">
+        <v>350</v>
+      </c>
+      <c r="H103" t="s">
+        <v>331</v>
+      </c>
+      <c r="I103" t="s">
+        <v>351</v>
+      </c>
+      <c r="J103" t="s">
+        <v>263</v>
+      </c>
+      <c r="K103">
+        <v>-16.304466999999999</v>
+      </c>
+      <c r="L103">
+        <v>-71.576599000000002</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A104" t="s">
+        <v>352</v>
+      </c>
+      <c r="B104" s="8">
+        <v>46007</v>
+      </c>
+      <c r="C104" s="8">
+        <v>46005</v>
+      </c>
+      <c r="D104" t="s">
+        <v>79</v>
+      </c>
+      <c r="E104" t="s">
+        <v>353</v>
+      </c>
+      <c r="F104" t="s">
+        <v>354</v>
+      </c>
+      <c r="G104" t="s">
+        <v>51</v>
+      </c>
+      <c r="H104" t="s">
+        <v>20</v>
+      </c>
+      <c r="I104" t="s">
+        <v>52</v>
+      </c>
+      <c r="J104" t="s">
+        <v>263</v>
+      </c>
+      <c r="K104">
+        <v>-12.874426</v>
+      </c>
+      <c r="L104">
+        <v>-74.397784000000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A105" t="s">
+        <v>355</v>
+      </c>
+      <c r="B105" s="8">
+        <v>46007</v>
+      </c>
+      <c r="C105" s="8">
+        <v>46007</v>
+      </c>
+      <c r="D105" t="s">
+        <v>68</v>
+      </c>
+      <c r="E105" t="s">
+        <v>68</v>
+      </c>
+      <c r="F105" t="s">
+        <v>356</v>
+      </c>
+      <c r="G105" t="s">
+        <v>357</v>
+      </c>
+      <c r="H105" t="s">
+        <v>331</v>
+      </c>
+      <c r="I105" t="s">
+        <v>351</v>
+      </c>
+      <c r="J105" t="s">
+        <v>263</v>
+      </c>
+      <c r="K105">
+        <v>-12.072317999999999</v>
+      </c>
+      <c r="L105">
+        <v>-77.017370999999997</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A106" t="s">
+        <v>358</v>
+      </c>
+      <c r="B106" s="8">
+        <v>46007</v>
+      </c>
+      <c r="C106" s="8">
+        <v>46004</v>
+      </c>
+      <c r="D106" t="s">
+        <v>48</v>
+      </c>
+      <c r="E106" t="s">
+        <v>359</v>
+      </c>
+      <c r="F106" t="s">
+        <v>360</v>
+      </c>
+      <c r="G106" t="s">
+        <v>361</v>
+      </c>
+      <c r="H106" t="s">
+        <v>20</v>
+      </c>
+      <c r="I106" t="s">
+        <v>283</v>
+      </c>
+      <c r="J106" t="s">
+        <v>263</v>
+      </c>
+      <c r="K106">
+        <v>-4.7979390000000004</v>
+      </c>
+      <c r="L106">
+        <v>-73.405101000000002</v>
+      </c>
+    </row>
     <row r="107" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="108" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="109" spans="1:12" ht="15.75" customHeight="1"/>
@@ -7297,7 +7634,7 @@
         <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -7385,7 +7722,7 @@
         <v>198</v>
       </c>
       <c r="B16" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="F16">
         <v>4</v>
@@ -7623,7 +7960,7 @@
         <v>289</v>
       </c>
       <c r="B30" t="s">
-        <v>306</v>
+        <v>363</v>
       </c>
       <c r="C30">
         <v>1</v>

--- a/emergencias.xlsx
+++ b/emergencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whuatay\Documents\TDOCUMENTOS\2025\COE MIDIS\Aplicativo_web\6. COE_TABLERO_SEMANAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F6ABB8-BA0C-4062-B37F-801185739776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690044FC-7EE1-4FFA-BB37-326FC3C89E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">events!$A$2:$L$96</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">impacto_programa!$A$1:$H$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">impacto_programa!$A$1:$H$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="419">
   <si>
     <t>fecha</t>
   </si>
@@ -1132,6 +1132,172 @@
   </si>
   <si>
     <t>PENSIÓN 65</t>
+  </si>
+  <si>
+    <t>EV_2025_106</t>
+  </si>
+  <si>
+    <t>Daños a vía de transporte (Santa María – Santa Teresa) en el caserío Cocalmayo. Vía bloqueada</t>
+  </si>
+  <si>
+    <t>EV_2025_107</t>
+  </si>
+  <si>
+    <t>Oxapampa</t>
+  </si>
+  <si>
+    <t>Villa Rica</t>
+  </si>
+  <si>
+    <t>Daños materiales (09 viviendas) en el sector Mellizos</t>
+  </si>
+  <si>
+    <t>EV_2025_108</t>
+  </si>
+  <si>
+    <t>Sihuas</t>
+  </si>
+  <si>
+    <t>Quiches</t>
+  </si>
+  <si>
+    <t>Daños materiales (01 vivienda) en el centro poblado Jocosbamba</t>
+  </si>
+  <si>
+    <t>FONCODES: La UT realiza el seguimiento correspondiente</t>
+  </si>
+  <si>
+    <t>EV_2025_109</t>
+  </si>
+  <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
+    <t>Daños a medios de vida (agricultura) en el centro poblado Pichiu San Pedro</t>
+  </si>
+  <si>
+    <t>EV_2025_110</t>
+  </si>
+  <si>
+    <t>Ranracancha</t>
+  </si>
+  <si>
+    <t>Daños a infraestructuras en diversos puntos del distrito</t>
+  </si>
+  <si>
+    <t>FONCODES: La UT informó que no se reportan daños a sus usuarios</t>
+  </si>
+  <si>
+    <t>EV_2025_111</t>
+  </si>
+  <si>
+    <t>Sandia</t>
+  </si>
+  <si>
+    <t>Daños a vías de transporte (Sandia-Mororia y Sandia-Apabuco)</t>
+  </si>
+  <si>
+    <t>EV_2025_112</t>
+  </si>
+  <si>
+    <t>Huachón</t>
+  </si>
+  <si>
+    <t>Daños materiales (09 viviendas) en la localidad Matriz de Huachón</t>
+  </si>
+  <si>
+    <t>PN PENSION 65: La UT informó que no registra afectación</t>
+  </si>
+  <si>
+    <t>EV_2025_113</t>
+  </si>
+  <si>
+    <t>Cosme</t>
+  </si>
+  <si>
+    <t>Daños materiales (01 vivienda) en el anexo de Santa Clara</t>
+  </si>
+  <si>
+    <t>EV_2025_114</t>
+  </si>
+  <si>
+    <t>Chanchamayo</t>
+  </si>
+  <si>
+    <t>Pichanaqui</t>
+  </si>
+  <si>
+    <t>Daños a la vida y salud de las personas (02 fallecidos y 12 heridos) a la altura del Jirón 1 de Mayo</t>
+  </si>
+  <si>
+    <t>EV_2025_115</t>
+  </si>
+  <si>
+    <t>Llumpa</t>
+  </si>
+  <si>
+    <t>Daños a cultivos, piscigranja, red de agua potable puente vehicular</t>
+  </si>
+  <si>
+    <t>EV_2025_116</t>
+  </si>
+  <si>
+    <t>Amarilis</t>
+  </si>
+  <si>
+    <t>13 casos de EDAS en el Comité de Gestión Virgen Del tránsito</t>
+  </si>
+  <si>
+    <t>PN CUNA MÁS: La UT realiza el seguimiento de los casos en coordinación con el sector salud</t>
+  </si>
+  <si>
+    <t>EV_2025_117</t>
+  </si>
+  <si>
+    <t>Daños a la vida y salud de las personas (20 heridos) por colisión vehicular múltiple entre buses de
+transporte público y privado</t>
+  </si>
+  <si>
+    <t>EV_2025_118</t>
+  </si>
+  <si>
+    <t>Camaná</t>
+  </si>
+  <si>
+    <t>Daños materiales (01 vivienda afectada ) y medios de vida en la zona urbana de Camaná</t>
+  </si>
+  <si>
+    <t>EV_2025_119</t>
+  </si>
+  <si>
+    <t>Alto Selva Alegre</t>
+  </si>
+  <si>
+    <t>Daños materiales (03 viviendas afectadas) en el caserío Selva Alegre</t>
+  </si>
+  <si>
+    <t>EV_2025_120</t>
+  </si>
+  <si>
+    <t>Mariscal Nieto</t>
+  </si>
+  <si>
+    <t>Daños materiales (01 vivienda afectada) en la zona urbana de Moquegua</t>
+  </si>
+  <si>
+    <t>PNP65: 01 usuaria afectada</t>
+  </si>
+  <si>
+    <t>EV_2025_121</t>
+  </si>
+  <si>
+    <t>Churubamba</t>
+  </si>
+  <si>
+    <t>Peligro inminente a 03 usuarios de PN Cuna Más en el centro poblado Matara</t>
+  </si>
+  <si>
+    <t>PN Cuna Más: La UT realiza el seguimiento de los casos en coordinación con el INDECI</t>
   </si>
 </sst>
 </file>
@@ -6538,28 +6704,620 @@
         <v>-73.405101000000002</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="108" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="109" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="110" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="111" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="112" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="107" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A107" t="s">
+        <v>364</v>
+      </c>
+      <c r="B107" s="8">
+        <v>46008</v>
+      </c>
+      <c r="C107" s="8">
+        <v>46008</v>
+      </c>
+      <c r="D107" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107" t="s">
+        <v>26</v>
+      </c>
+      <c r="G107" t="s">
+        <v>272</v>
+      </c>
+      <c r="H107" t="s">
+        <v>28</v>
+      </c>
+      <c r="I107" t="s">
+        <v>365</v>
+      </c>
+      <c r="J107" t="s">
+        <v>263</v>
+      </c>
+      <c r="K107">
+        <v>-13.244382</v>
+      </c>
+      <c r="L107">
+        <v>-72.732980999999995</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A108" t="s">
+        <v>366</v>
+      </c>
+      <c r="B108" s="8">
+        <v>46008</v>
+      </c>
+      <c r="C108" s="8">
+        <v>46006</v>
+      </c>
+      <c r="D108" t="s">
+        <v>44</v>
+      </c>
+      <c r="E108" t="s">
+        <v>367</v>
+      </c>
+      <c r="F108" t="s">
+        <v>368</v>
+      </c>
+      <c r="G108" t="s">
+        <v>248</v>
+      </c>
+      <c r="H108" t="s">
+        <v>20</v>
+      </c>
+      <c r="I108" t="s">
+        <v>369</v>
+      </c>
+      <c r="J108" t="s">
+        <v>263</v>
+      </c>
+      <c r="K108">
+        <v>-10.634198</v>
+      </c>
+      <c r="L108">
+        <v>-75.175914000000006</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A109" t="s">
+        <v>370</v>
+      </c>
+      <c r="B109" s="8">
+        <v>46008</v>
+      </c>
+      <c r="C109" s="8">
+        <v>46006</v>
+      </c>
+      <c r="D109" t="s">
+        <v>133</v>
+      </c>
+      <c r="E109" t="s">
+        <v>371</v>
+      </c>
+      <c r="F109" t="s">
+        <v>372</v>
+      </c>
+      <c r="G109" t="s">
+        <v>51</v>
+      </c>
+      <c r="H109" t="s">
+        <v>20</v>
+      </c>
+      <c r="I109" t="s">
+        <v>373</v>
+      </c>
+      <c r="J109" t="s">
+        <v>374</v>
+      </c>
+      <c r="K109">
+        <v>-8.3959790000000005</v>
+      </c>
+      <c r="L109">
+        <v>-77.509755999999996</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A110" t="s">
+        <v>375</v>
+      </c>
+      <c r="B110" s="8">
+        <v>46008</v>
+      </c>
+      <c r="C110" s="8">
+        <v>46006</v>
+      </c>
+      <c r="D110" t="s">
+        <v>133</v>
+      </c>
+      <c r="E110" t="s">
+        <v>285</v>
+      </c>
+      <c r="F110" t="s">
+        <v>376</v>
+      </c>
+      <c r="G110" t="s">
+        <v>287</v>
+      </c>
+      <c r="H110" t="s">
+        <v>20</v>
+      </c>
+      <c r="I110" t="s">
+        <v>377</v>
+      </c>
+      <c r="J110" t="s">
+        <v>374</v>
+      </c>
+      <c r="K110">
+        <v>-9.628152</v>
+      </c>
+      <c r="L110">
+        <v>-77.091897000000003</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A111" t="s">
+        <v>378</v>
+      </c>
+      <c r="B111" s="8">
+        <v>46008</v>
+      </c>
+      <c r="C111" s="8">
+        <v>46008</v>
+      </c>
+      <c r="D111" t="s">
+        <v>35</v>
+      </c>
+      <c r="E111" t="s">
+        <v>319</v>
+      </c>
+      <c r="F111" t="s">
+        <v>379</v>
+      </c>
+      <c r="G111" t="s">
+        <v>58</v>
+      </c>
+      <c r="H111" t="s">
+        <v>331</v>
+      </c>
+      <c r="I111" t="s">
+        <v>380</v>
+      </c>
+      <c r="J111" t="s">
+        <v>381</v>
+      </c>
+      <c r="K111">
+        <v>-13.244382</v>
+      </c>
+      <c r="L111">
+        <v>-72.732980999999995</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A112" t="s">
+        <v>382</v>
+      </c>
+      <c r="B112" s="8">
+        <v>46008</v>
+      </c>
+      <c r="C112" s="8">
+        <v>46007</v>
+      </c>
+      <c r="D112" t="s">
+        <v>54</v>
+      </c>
+      <c r="E112" t="s">
+        <v>383</v>
+      </c>
+      <c r="F112" t="s">
+        <v>383</v>
+      </c>
+      <c r="G112" t="s">
+        <v>272</v>
+      </c>
+      <c r="H112" t="s">
+        <v>20</v>
+      </c>
+      <c r="I112" t="s">
+        <v>384</v>
+      </c>
+      <c r="J112" t="s">
+        <v>381</v>
+      </c>
+      <c r="K112">
+        <v>-14.291931</v>
+      </c>
+      <c r="L112">
+        <v>-69.436959999999999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A113" t="s">
+        <v>385</v>
+      </c>
+      <c r="B113" s="8">
+        <v>46009</v>
+      </c>
+      <c r="C113" s="8">
+        <v>46008</v>
+      </c>
+      <c r="D113" t="s">
+        <v>44</v>
+      </c>
+      <c r="E113" t="s">
+        <v>44</v>
+      </c>
+      <c r="F113" t="s">
+        <v>386</v>
+      </c>
+      <c r="G113" t="s">
+        <v>81</v>
+      </c>
+      <c r="H113" t="s">
+        <v>20</v>
+      </c>
+      <c r="I113" t="s">
+        <v>387</v>
+      </c>
+      <c r="J113" t="s">
+        <v>388</v>
+      </c>
+      <c r="K113">
+        <v>-10.574252</v>
+      </c>
+      <c r="L113">
+        <v>-75.785488000000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A114" t="s">
+        <v>389</v>
+      </c>
+      <c r="B114" s="8">
+        <v>46009</v>
+      </c>
+      <c r="C114" s="8">
+        <v>46008</v>
+      </c>
+      <c r="D114" t="s">
+        <v>79</v>
+      </c>
+      <c r="E114" t="s">
+        <v>89</v>
+      </c>
+      <c r="F114" t="s">
+        <v>390</v>
+      </c>
+      <c r="G114" t="s">
+        <v>58</v>
+      </c>
+      <c r="H114" t="s">
+        <v>20</v>
+      </c>
+      <c r="I114" t="s">
+        <v>391</v>
+      </c>
+      <c r="J114" t="s">
+        <v>22</v>
+      </c>
+      <c r="K114">
+        <v>-12.570512000000001</v>
+      </c>
+      <c r="L114">
+        <v>-74.645240999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A115" t="s">
+        <v>392</v>
+      </c>
+      <c r="B115" s="8">
+        <v>46009</v>
+      </c>
+      <c r="C115" s="8">
+        <v>46009</v>
+      </c>
+      <c r="D115" t="s">
+        <v>294</v>
+      </c>
+      <c r="E115" t="s">
+        <v>393</v>
+      </c>
+      <c r="F115" t="s">
+        <v>394</v>
+      </c>
+      <c r="G115" t="s">
+        <v>317</v>
+      </c>
+      <c r="H115" t="s">
+        <v>28</v>
+      </c>
+      <c r="I115" t="s">
+        <v>395</v>
+      </c>
+      <c r="J115" t="s">
+        <v>22</v>
+      </c>
+      <c r="K115">
+        <v>-11.025029999999999</v>
+      </c>
+      <c r="L115">
+        <v>-74.868764999999996</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A116" t="s">
+        <v>396</v>
+      </c>
+      <c r="B116" s="8">
+        <v>46009</v>
+      </c>
+      <c r="C116" s="8">
+        <v>46008</v>
+      </c>
+      <c r="D116" t="s">
+        <v>133</v>
+      </c>
+      <c r="E116" t="s">
+        <v>162</v>
+      </c>
+      <c r="F116" t="s">
+        <v>397</v>
+      </c>
+      <c r="G116" t="s">
+        <v>58</v>
+      </c>
+      <c r="H116" t="s">
+        <v>331</v>
+      </c>
+      <c r="I116" t="s">
+        <v>398</v>
+      </c>
+      <c r="J116" t="s">
+        <v>22</v>
+      </c>
+      <c r="K116">
+        <v>-8.9674809999999994</v>
+      </c>
+      <c r="L116">
+        <v>-77.456372999999999</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A117" t="s">
+        <v>399</v>
+      </c>
+      <c r="B117" s="8">
+        <v>46009</v>
+      </c>
+      <c r="C117" s="8">
+        <v>46009</v>
+      </c>
+      <c r="D117" t="s">
+        <v>17</v>
+      </c>
+      <c r="E117" t="s">
+        <v>17</v>
+      </c>
+      <c r="F117" t="s">
+        <v>400</v>
+      </c>
+      <c r="G117" t="s">
+        <v>350</v>
+      </c>
+      <c r="H117" t="s">
+        <v>331</v>
+      </c>
+      <c r="I117" t="s">
+        <v>401</v>
+      </c>
+      <c r="J117" t="s">
+        <v>402</v>
+      </c>
+      <c r="K117">
+        <v>-16.304466999999999</v>
+      </c>
+      <c r="L117">
+        <v>-71.576599000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A118" t="s">
+        <v>403</v>
+      </c>
+      <c r="B118" s="8">
+        <v>46010</v>
+      </c>
+      <c r="C118" s="8">
+        <v>46010</v>
+      </c>
+      <c r="D118" t="s">
+        <v>68</v>
+      </c>
+      <c r="E118" t="s">
+        <v>68</v>
+      </c>
+      <c r="F118" t="s">
+        <v>313</v>
+      </c>
+      <c r="G118" t="s">
+        <v>317</v>
+      </c>
+      <c r="H118" t="s">
+        <v>331</v>
+      </c>
+      <c r="I118" t="s">
+        <v>404</v>
+      </c>
+      <c r="J118" t="s">
+        <v>22</v>
+      </c>
+      <c r="K118">
+        <v>-11.987477</v>
+      </c>
+      <c r="L118">
+        <v>-77.046008</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A119" t="s">
+        <v>405</v>
+      </c>
+      <c r="B119" s="8">
+        <v>46010</v>
+      </c>
+      <c r="C119" s="8">
+        <v>46008</v>
+      </c>
+      <c r="D119" t="s">
+        <v>348</v>
+      </c>
+      <c r="E119" t="s">
+        <v>406</v>
+      </c>
+      <c r="F119" t="s">
+        <v>406</v>
+      </c>
+      <c r="G119" t="s">
+        <v>357</v>
+      </c>
+      <c r="H119" t="s">
+        <v>20</v>
+      </c>
+      <c r="I119" t="s">
+        <v>407</v>
+      </c>
+      <c r="J119" t="s">
+        <v>22</v>
+      </c>
+      <c r="K119">
+        <v>-16.630914000000001</v>
+      </c>
+      <c r="L119">
+        <v>-72.712879999999998</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A120" t="s">
+        <v>408</v>
+      </c>
+      <c r="B120" s="8">
+        <v>46010</v>
+      </c>
+      <c r="C120" s="8">
+        <v>46009</v>
+      </c>
+      <c r="D120" t="s">
+        <v>348</v>
+      </c>
+      <c r="E120" t="s">
+        <v>348</v>
+      </c>
+      <c r="F120" t="s">
+        <v>409</v>
+      </c>
+      <c r="G120" t="s">
+        <v>357</v>
+      </c>
+      <c r="H120" t="s">
+        <v>20</v>
+      </c>
+      <c r="I120" t="s">
+        <v>410</v>
+      </c>
+      <c r="J120" t="s">
+        <v>22</v>
+      </c>
+      <c r="K120">
+        <v>-16.330962</v>
+      </c>
+      <c r="L120">
+        <v>-71.485857999999993</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A121" t="s">
+        <v>411</v>
+      </c>
+      <c r="B121" s="8">
+        <v>46010</v>
+      </c>
+      <c r="C121" s="8">
+        <v>46009</v>
+      </c>
+      <c r="D121" t="s">
+        <v>177</v>
+      </c>
+      <c r="E121" t="s">
+        <v>412</v>
+      </c>
+      <c r="F121" t="s">
+        <v>177</v>
+      </c>
+      <c r="G121" t="s">
+        <v>357</v>
+      </c>
+      <c r="H121" t="s">
+        <v>20</v>
+      </c>
+      <c r="I121" t="s">
+        <v>413</v>
+      </c>
+      <c r="J121" t="s">
+        <v>414</v>
+      </c>
+      <c r="K121">
+        <v>-17.217707999999998</v>
+      </c>
+      <c r="L121">
+        <v>-71.064747999999994</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A122" t="s">
+        <v>415</v>
+      </c>
+      <c r="B122" s="8">
+        <v>46010</v>
+      </c>
+      <c r="C122" s="8">
+        <v>46008</v>
+      </c>
+      <c r="D122" t="s">
+        <v>17</v>
+      </c>
+      <c r="E122" t="s">
+        <v>17</v>
+      </c>
+      <c r="F122" t="s">
+        <v>416</v>
+      </c>
+      <c r="G122" t="s">
+        <v>248</v>
+      </c>
+      <c r="H122" t="s">
+        <v>20</v>
+      </c>
+      <c r="I122" t="s">
+        <v>417</v>
+      </c>
+      <c r="J122" t="s">
+        <v>418</v>
+      </c>
+      <c r="K122">
+        <v>-9.6852610000000006</v>
+      </c>
+      <c r="L122">
+        <v>-76.265728999999993</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="124" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="125" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="126" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
     <row r="131" ht="15.75" customHeight="1"/>
@@ -7440,7 +8198,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:H999"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
@@ -7785,7 +8543,7 @@
         <v>45989</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" t="s">
         <v>217</v>
       </c>
@@ -7972,7 +8730,26 @@
         <v>46001</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A31" t="s">
+        <v>355</v>
+      </c>
+      <c r="B31" t="s">
+        <v>324</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>43</v>
+      </c>
+      <c r="G31">
+        <v>46007</v>
+      </c>
+      <c r="H31">
+        <v>46007</v>
+      </c>
+    </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -8941,7 +9718,6 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H30">
     <sortCondition ref="A2:A30"/>

--- a/emergencias.xlsx
+++ b/emergencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whuatay\Documents\TDOCUMENTOS\2025\COE MIDIS\Aplicativo_web\6. COE_TABLERO_SEMANAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690044FC-7EE1-4FFA-BB37-326FC3C89E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B30091-A577-4EF1-A9AC-6A4AD0066426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="423">
   <si>
     <t>fecha</t>
   </si>
@@ -1298,6 +1298,18 @@
   </si>
   <si>
     <t>PN Cuna Más: La UT realiza el seguimiento de los casos en coordinación con el INDECI</t>
+  </si>
+  <si>
+    <t>EV_2025_122</t>
+  </si>
+  <si>
+    <t>Leoncio Prado</t>
+  </si>
+  <si>
+    <t>Luyando</t>
+  </si>
+  <si>
+    <t>1 Local educativo afectado.</t>
   </si>
 </sst>
 </file>
@@ -7312,7 +7324,44 @@
         <v>-76.265728999999993</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="123" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A123" t="s">
+        <v>419</v>
+      </c>
+      <c r="B123" s="8">
+        <v>46010</v>
+      </c>
+      <c r="C123" s="8">
+        <v>46010</v>
+      </c>
+      <c r="D123" t="s">
+        <v>17</v>
+      </c>
+      <c r="E123" t="s">
+        <v>420</v>
+      </c>
+      <c r="F123" t="s">
+        <v>421</v>
+      </c>
+      <c r="G123" t="s">
+        <v>19</v>
+      </c>
+      <c r="H123" t="s">
+        <v>331</v>
+      </c>
+      <c r="I123" t="s">
+        <v>422</v>
+      </c>
+      <c r="J123" t="s">
+        <v>22</v>
+      </c>
+      <c r="K123">
+        <v>-9.2406559999999995</v>
+      </c>
+      <c r="L123">
+        <v>-75.953225000000003</v>
+      </c>
+    </row>
     <row r="124" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="125" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="126" spans="1:12" ht="15.75" customHeight="1"/>
@@ -8750,7 +8799,17 @@
         <v>46007</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A32" t="s">
+        <v>411</v>
+      </c>
+      <c r="B32" t="s">
+        <v>363</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>

--- a/emergencias.xlsx
+++ b/emergencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whuatay\Documents\TDOCUMENTOS\2025\COE MIDIS\Aplicativo_web\6. COE_TABLERO_SEMANAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B30091-A577-4EF1-A9AC-6A4AD0066426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194BB16C-8140-48B9-8CB1-041743A571F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="impacto_programa" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">events!$A$2:$L$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">events!$A$1:$L$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">impacto_programa!$A$1:$H$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="463">
   <si>
     <t>fecha</t>
   </si>
@@ -1023,9 +1023,6 @@
     <t>EV_2025_96</t>
   </si>
   <si>
-    <t>Belen</t>
-  </si>
-  <si>
     <t>Personas damnificadas y viviendas destruidas</t>
   </si>
   <si>
@@ -1087,9 +1084,6 @@
   </si>
   <si>
     <t>Arequipa</t>
-  </si>
-  <si>
-    <t>Cerro colorado</t>
   </si>
   <si>
     <t>Enfermedades virales</t>
@@ -1310,6 +1304,132 @@
   </si>
   <si>
     <t>1 Local educativo afectado.</t>
+  </si>
+  <si>
+    <t>Cerro Colorado</t>
+  </si>
+  <si>
+    <t>Belén</t>
+  </si>
+  <si>
+    <t>EV_2025_123</t>
+  </si>
+  <si>
+    <t>Castrovirreyna</t>
+  </si>
+  <si>
+    <t>Ticrapo</t>
+  </si>
+  <si>
+    <t>Daños a la vida y salud de las personas (01 usuaria PNCM herida y 01 Madre de usuaria PNCM fallecida) en la vía nacional Ticrapo-Mollepampa</t>
+  </si>
+  <si>
+    <t>PN Cuna Más: La UT realiza el seguimiento de los casos en coordinación con las autoridades competentes</t>
+  </si>
+  <si>
+    <t>EV_2025_124</t>
+  </si>
+  <si>
+    <t>Madre de Dios</t>
+  </si>
+  <si>
+    <t>Tambopata</t>
+  </si>
+  <si>
+    <t>Laberinto</t>
+  </si>
+  <si>
+    <t>Daños materiales (local destruido) en el jirón 08 de Octubre</t>
+  </si>
+  <si>
+    <t>EV_2025_125</t>
+  </si>
+  <si>
+    <t>Daños materiales (vías afectadas) en la localidad Bajo Pichanaqui</t>
+  </si>
+  <si>
+    <t>EV_2025_126</t>
+  </si>
+  <si>
+    <t>Ica</t>
+  </si>
+  <si>
+    <t>Nasca</t>
+  </si>
+  <si>
+    <t>Vista Alegre</t>
+  </si>
+  <si>
+    <t>Daños materiales (01 vivienda afectada) en el A.H. Los Giraloses</t>
+  </si>
+  <si>
+    <t>EV_2025_127</t>
+  </si>
+  <si>
+    <t>Calca</t>
+  </si>
+  <si>
+    <t>Yanatile</t>
+  </si>
+  <si>
+    <t>Daños materiales (01 puente destruido) por la crecida del río Oscobamba en el CP Colca</t>
+  </si>
+  <si>
+    <t>CET CUSCO: Coordina con los JUT de la región el monitoreo de la emergencia</t>
+  </si>
+  <si>
+    <t>EV_2025_128</t>
+  </si>
+  <si>
+    <t>Ocumal</t>
+  </si>
+  <si>
+    <t>Daños materiales (02 viviendas afectadas) en el anexo Cuichima</t>
+  </si>
+  <si>
+    <t>EV_2025_129</t>
+  </si>
+  <si>
+    <t>Huaylas</t>
+  </si>
+  <si>
+    <t>Pueblo Libre</t>
+  </si>
+  <si>
+    <t>Daños a cobertura natural en el sector Huerapampa</t>
+  </si>
+  <si>
+    <t>EV_2025_130</t>
+  </si>
+  <si>
+    <t>Rimac</t>
+  </si>
+  <si>
+    <t>Daños a almacén</t>
+  </si>
+  <si>
+    <t>01 almacén afectado</t>
+  </si>
+  <si>
+    <t>EV_2025_131</t>
+  </si>
+  <si>
+    <t>Daños materiales</t>
+  </si>
+  <si>
+    <t>Ancash</t>
+  </si>
+  <si>
+    <t>Santa</t>
+  </si>
+  <si>
+    <t>Chimbote</t>
+  </si>
+  <si>
+    <t>EV_2025_132</t>
+  </si>
+  <si>
+    <t>Manu</t>
   </si>
 </sst>
 </file>
@@ -1319,11 +1439,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-280A]hh:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1364,7 +1491,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1372,32 +1499,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2655,8 +2807,7 @@
     <col min="2" max="2" width="15.85546875" customWidth="1"/>
     <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="5" max="6" width="21.42578125" customWidth="1"/>
     <col min="7" max="7" width="33.28515625" customWidth="1"/>
     <col min="8" max="8" width="18.140625" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
@@ -6353,7 +6504,7 @@
         <v>49</v>
       </c>
       <c r="F97" t="s">
-        <v>327</v>
+        <v>422</v>
       </c>
       <c r="G97" t="s">
         <v>94</v>
@@ -6362,7 +6513,7 @@
         <v>20</v>
       </c>
       <c r="I97" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J97" t="s">
         <v>263</v>
@@ -6376,7 +6527,7 @@
     </row>
     <row r="98" spans="1:12" ht="15.75" customHeight="1">
       <c r="A98" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B98" s="8">
         <v>46006</v>
@@ -6391,19 +6542,19 @@
         <v>25</v>
       </c>
       <c r="F98" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G98" t="s">
         <v>167</v>
       </c>
       <c r="H98" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I98" t="s">
         <v>251</v>
       </c>
       <c r="J98" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K98">
         <v>-12.355022</v>
@@ -6414,7 +6565,7 @@
     </row>
     <row r="99" spans="1:12" ht="15.75" customHeight="1">
       <c r="A99" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B99" s="8">
         <v>46006</v>
@@ -6423,13 +6574,13 @@
         <v>46004</v>
       </c>
       <c r="D99" t="s">
+        <v>333</v>
+      </c>
+      <c r="E99" t="s">
+        <v>333</v>
+      </c>
+      <c r="F99" t="s">
         <v>334</v>
-      </c>
-      <c r="E99" t="s">
-        <v>334</v>
-      </c>
-      <c r="F99" t="s">
-        <v>335</v>
       </c>
       <c r="G99" t="s">
         <v>248</v>
@@ -6438,10 +6589,10 @@
         <v>20</v>
       </c>
       <c r="I99" t="s">
+        <v>335</v>
+      </c>
+      <c r="J99" t="s">
         <v>336</v>
-      </c>
-      <c r="J99" t="s">
-        <v>337</v>
       </c>
       <c r="K99">
         <v>-12.355022</v>
@@ -6452,7 +6603,7 @@
     </row>
     <row r="100" spans="1:12" ht="15.75" customHeight="1">
       <c r="A100" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B100" s="8">
         <v>46006</v>
@@ -6461,13 +6612,13 @@
         <v>46004</v>
       </c>
       <c r="D100" t="s">
+        <v>333</v>
+      </c>
+      <c r="E100" t="s">
+        <v>333</v>
+      </c>
+      <c r="F100" t="s">
         <v>334</v>
-      </c>
-      <c r="E100" t="s">
-        <v>334</v>
-      </c>
-      <c r="F100" t="s">
-        <v>335</v>
       </c>
       <c r="G100" t="s">
         <v>248</v>
@@ -6476,10 +6627,10 @@
         <v>20</v>
       </c>
       <c r="I100" t="s">
+        <v>335</v>
+      </c>
+      <c r="J100" t="s">
         <v>336</v>
-      </c>
-      <c r="J100" t="s">
-        <v>337</v>
       </c>
       <c r="K100">
         <v>-11.879155000000001</v>
@@ -6490,7 +6641,7 @@
     </row>
     <row r="101" spans="1:12" ht="15.75" customHeight="1">
       <c r="A101" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B101" s="8">
         <v>46006</v>
@@ -6502,19 +6653,19 @@
         <v>84</v>
       </c>
       <c r="E101" t="s">
+        <v>339</v>
+      </c>
+      <c r="F101" t="s">
         <v>340</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>341</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
+        <v>330</v>
+      </c>
+      <c r="I101" t="s">
         <v>342</v>
-      </c>
-      <c r="H101" t="s">
-        <v>331</v>
-      </c>
-      <c r="I101" t="s">
-        <v>343</v>
       </c>
       <c r="J101" t="s">
         <v>263</v>
@@ -6528,7 +6679,7 @@
     </row>
     <row r="102" spans="1:12" ht="15.75" customHeight="1">
       <c r="A102" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B102" s="8">
         <v>46007</v>
@@ -6543,16 +6694,16 @@
         <v>44</v>
       </c>
       <c r="F102" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G102" t="s">
         <v>51</v>
       </c>
       <c r="H102" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I102" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J102" t="s">
         <v>263</v>
@@ -6566,7 +6717,7 @@
     </row>
     <row r="103" spans="1:12" ht="15.75" customHeight="1">
       <c r="A103" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B103" s="8">
         <v>46007</v>
@@ -6575,22 +6726,22 @@
         <v>46007</v>
       </c>
       <c r="D103" t="s">
+        <v>347</v>
+      </c>
+      <c r="E103" t="s">
+        <v>347</v>
+      </c>
+      <c r="F103" t="s">
+        <v>421</v>
+      </c>
+      <c r="G103" t="s">
         <v>348</v>
       </c>
-      <c r="E103" t="s">
-        <v>348</v>
-      </c>
-      <c r="F103" t="s">
+      <c r="H103" t="s">
+        <v>330</v>
+      </c>
+      <c r="I103" t="s">
         <v>349</v>
-      </c>
-      <c r="G103" t="s">
-        <v>350</v>
-      </c>
-      <c r="H103" t="s">
-        <v>331</v>
-      </c>
-      <c r="I103" t="s">
-        <v>351</v>
       </c>
       <c r="J103" t="s">
         <v>263</v>
@@ -6604,7 +6755,7 @@
     </row>
     <row r="104" spans="1:12" ht="15.75" customHeight="1">
       <c r="A104" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B104" s="8">
         <v>46007</v>
@@ -6616,10 +6767,10 @@
         <v>79</v>
       </c>
       <c r="E104" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F104" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G104" t="s">
         <v>51</v>
@@ -6642,7 +6793,7 @@
     </row>
     <row r="105" spans="1:12" ht="15.75" customHeight="1">
       <c r="A105" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B105" s="8">
         <v>46007</v>
@@ -6657,16 +6808,16 @@
         <v>68</v>
       </c>
       <c r="F105" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G105" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H105" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I105" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J105" t="s">
         <v>263</v>
@@ -6680,7 +6831,7 @@
     </row>
     <row r="106" spans="1:12" ht="15.75" customHeight="1">
       <c r="A106" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B106" s="8">
         <v>46007</v>
@@ -6692,13 +6843,13 @@
         <v>48</v>
       </c>
       <c r="E106" t="s">
+        <v>357</v>
+      </c>
+      <c r="F106" t="s">
+        <v>358</v>
+      </c>
+      <c r="G106" t="s">
         <v>359</v>
-      </c>
-      <c r="F106" t="s">
-        <v>360</v>
-      </c>
-      <c r="G106" t="s">
-        <v>361</v>
       </c>
       <c r="H106" t="s">
         <v>20</v>
@@ -6718,7 +6869,7 @@
     </row>
     <row r="107" spans="1:12" ht="15.75" customHeight="1">
       <c r="A107" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B107" s="8">
         <v>46008</v>
@@ -6742,7 +6893,7 @@
         <v>28</v>
       </c>
       <c r="I107" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="J107" t="s">
         <v>263</v>
@@ -6756,7 +6907,7 @@
     </row>
     <row r="108" spans="1:12" ht="15.75" customHeight="1">
       <c r="A108" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B108" s="8">
         <v>46008</v>
@@ -6768,10 +6919,10 @@
         <v>44</v>
       </c>
       <c r="E108" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F108" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G108" t="s">
         <v>248</v>
@@ -6780,7 +6931,7 @@
         <v>20</v>
       </c>
       <c r="I108" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J108" t="s">
         <v>263</v>
@@ -6794,7 +6945,7 @@
     </row>
     <row r="109" spans="1:12" ht="15.75" customHeight="1">
       <c r="A109" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B109" s="8">
         <v>46008</v>
@@ -6806,10 +6957,10 @@
         <v>133</v>
       </c>
       <c r="E109" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F109" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G109" t="s">
         <v>51</v>
@@ -6818,10 +6969,10 @@
         <v>20</v>
       </c>
       <c r="I109" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="J109" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K109">
         <v>-8.3959790000000005</v>
@@ -6832,7 +6983,7 @@
     </row>
     <row r="110" spans="1:12" ht="15.75" customHeight="1">
       <c r="A110" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B110" s="8">
         <v>46008</v>
@@ -6847,7 +6998,7 @@
         <v>285</v>
       </c>
       <c r="F110" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G110" t="s">
         <v>287</v>
@@ -6856,10 +7007,10 @@
         <v>20</v>
       </c>
       <c r="I110" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J110" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="K110">
         <v>-9.628152</v>
@@ -6870,7 +7021,7 @@
     </row>
     <row r="111" spans="1:12" ht="15.75" customHeight="1">
       <c r="A111" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B111" s="8">
         <v>46008</v>
@@ -6885,19 +7036,19 @@
         <v>319</v>
       </c>
       <c r="F111" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G111" t="s">
         <v>58</v>
       </c>
       <c r="H111" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I111" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J111" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K111">
         <v>-13.244382</v>
@@ -6908,7 +7059,7 @@
     </row>
     <row r="112" spans="1:12" ht="15.75" customHeight="1">
       <c r="A112" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B112" s="8">
         <v>46008</v>
@@ -6920,10 +7071,10 @@
         <v>54</v>
       </c>
       <c r="E112" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F112" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G112" t="s">
         <v>272</v>
@@ -6932,10 +7083,10 @@
         <v>20</v>
       </c>
       <c r="I112" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J112" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K112">
         <v>-14.291931</v>
@@ -6946,7 +7097,7 @@
     </row>
     <row r="113" spans="1:12" ht="15.75" customHeight="1">
       <c r="A113" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B113" s="8">
         <v>46009</v>
@@ -6961,7 +7112,7 @@
         <v>44</v>
       </c>
       <c r="F113" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G113" t="s">
         <v>81</v>
@@ -6970,10 +7121,10 @@
         <v>20</v>
       </c>
       <c r="I113" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J113" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="K113">
         <v>-10.574252</v>
@@ -6984,7 +7135,7 @@
     </row>
     <row r="114" spans="1:12" ht="15.75" customHeight="1">
       <c r="A114" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B114" s="8">
         <v>46009</v>
@@ -6999,7 +7150,7 @@
         <v>89</v>
       </c>
       <c r="F114" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G114" t="s">
         <v>58</v>
@@ -7008,7 +7159,7 @@
         <v>20</v>
       </c>
       <c r="I114" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="J114" t="s">
         <v>22</v>
@@ -7022,7 +7173,7 @@
     </row>
     <row r="115" spans="1:12" ht="15.75" customHeight="1">
       <c r="A115" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B115" s="8">
         <v>46009</v>
@@ -7034,10 +7185,10 @@
         <v>294</v>
       </c>
       <c r="E115" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="F115" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G115" t="s">
         <v>317</v>
@@ -7046,7 +7197,7 @@
         <v>28</v>
       </c>
       <c r="I115" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J115" t="s">
         <v>22</v>
@@ -7060,7 +7211,7 @@
     </row>
     <row r="116" spans="1:12" ht="15.75" customHeight="1">
       <c r="A116" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B116" s="8">
         <v>46009</v>
@@ -7075,16 +7226,16 @@
         <v>162</v>
       </c>
       <c r="F116" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G116" t="s">
         <v>58</v>
       </c>
       <c r="H116" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I116" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="J116" t="s">
         <v>22</v>
@@ -7098,7 +7249,7 @@
     </row>
     <row r="117" spans="1:12" ht="15.75" customHeight="1">
       <c r="A117" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B117" s="8">
         <v>46009</v>
@@ -7113,19 +7264,19 @@
         <v>17</v>
       </c>
       <c r="F117" t="s">
+        <v>398</v>
+      </c>
+      <c r="G117" t="s">
+        <v>348</v>
+      </c>
+      <c r="H117" t="s">
+        <v>330</v>
+      </c>
+      <c r="I117" t="s">
+        <v>399</v>
+      </c>
+      <c r="J117" t="s">
         <v>400</v>
-      </c>
-      <c r="G117" t="s">
-        <v>350</v>
-      </c>
-      <c r="H117" t="s">
-        <v>331</v>
-      </c>
-      <c r="I117" t="s">
-        <v>401</v>
-      </c>
-      <c r="J117" t="s">
-        <v>402</v>
       </c>
       <c r="K117">
         <v>-16.304466999999999</v>
@@ -7136,7 +7287,7 @@
     </row>
     <row r="118" spans="1:12" ht="15.75" customHeight="1">
       <c r="A118" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B118" s="8">
         <v>46010</v>
@@ -7157,10 +7308,10 @@
         <v>317</v>
       </c>
       <c r="H118" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I118" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="J118" t="s">
         <v>22</v>
@@ -7174,7 +7325,7 @@
     </row>
     <row r="119" spans="1:12" ht="15.75" customHeight="1">
       <c r="A119" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B119" s="8">
         <v>46010</v>
@@ -7183,22 +7334,22 @@
         <v>46008</v>
       </c>
       <c r="D119" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E119" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F119" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G119" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H119" t="s">
         <v>20</v>
       </c>
       <c r="I119" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J119" t="s">
         <v>22</v>
@@ -7212,7 +7363,7 @@
     </row>
     <row r="120" spans="1:12" ht="15.75" customHeight="1">
       <c r="A120" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B120" s="8">
         <v>46010</v>
@@ -7221,22 +7372,22 @@
         <v>46009</v>
       </c>
       <c r="D120" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E120" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F120" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G120" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H120" t="s">
         <v>20</v>
       </c>
       <c r="I120" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J120" t="s">
         <v>22</v>
@@ -7250,7 +7401,7 @@
     </row>
     <row r="121" spans="1:12" ht="15.75" customHeight="1">
       <c r="A121" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B121" s="8">
         <v>46010</v>
@@ -7262,22 +7413,22 @@
         <v>177</v>
       </c>
       <c r="E121" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F121" t="s">
         <v>177</v>
       </c>
       <c r="G121" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H121" t="s">
         <v>20</v>
       </c>
       <c r="I121" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J121" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="K121">
         <v>-17.217707999999998</v>
@@ -7288,7 +7439,7 @@
     </row>
     <row r="122" spans="1:12" ht="15.75" customHeight="1">
       <c r="A122" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B122" s="8">
         <v>46010</v>
@@ -7303,7 +7454,7 @@
         <v>17</v>
       </c>
       <c r="F122" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G122" t="s">
         <v>248</v>
@@ -7312,10 +7463,10 @@
         <v>20</v>
       </c>
       <c r="I122" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="J122" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K122">
         <v>-9.6852610000000006</v>
@@ -7326,7 +7477,7 @@
     </row>
     <row r="123" spans="1:12" ht="15.75" customHeight="1">
       <c r="A123" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B123" s="8">
         <v>46010</v>
@@ -7338,19 +7489,19 @@
         <v>17</v>
       </c>
       <c r="E123" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F123" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G123" t="s">
         <v>19</v>
       </c>
       <c r="H123" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I123" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="J123" t="s">
         <v>22</v>
@@ -7362,27 +7513,397 @@
         <v>-75.953225000000003</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="125" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="126" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="127" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="124" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A124" t="s">
+        <v>423</v>
+      </c>
+      <c r="B124" s="8">
+        <v>46013</v>
+      </c>
+      <c r="C124" s="8">
+        <v>46011</v>
+      </c>
+      <c r="D124" t="s">
+        <v>79</v>
+      </c>
+      <c r="E124" t="s">
+        <v>424</v>
+      </c>
+      <c r="F124" t="s">
+        <v>425</v>
+      </c>
+      <c r="G124" t="s">
+        <v>317</v>
+      </c>
+      <c r="H124" t="s">
+        <v>20</v>
+      </c>
+      <c r="I124" t="s">
+        <v>426</v>
+      </c>
+      <c r="J124" t="s">
+        <v>427</v>
+      </c>
+      <c r="K124">
+        <v>-13.418063999999999</v>
+      </c>
+      <c r="L124">
+        <v>-75.409744000000003</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A125" t="s">
+        <v>428</v>
+      </c>
+      <c r="B125" s="8">
+        <v>46013</v>
+      </c>
+      <c r="C125" s="8">
+        <v>46013</v>
+      </c>
+      <c r="D125" t="s">
+        <v>429</v>
+      </c>
+      <c r="E125" t="s">
+        <v>430</v>
+      </c>
+      <c r="F125" t="s">
+        <v>431</v>
+      </c>
+      <c r="G125" t="s">
+        <v>94</v>
+      </c>
+      <c r="H125" t="s">
+        <v>28</v>
+      </c>
+      <c r="I125" t="s">
+        <v>432</v>
+      </c>
+      <c r="J125" t="s">
+        <v>22</v>
+      </c>
+      <c r="K125">
+        <v>-12.513322000000001</v>
+      </c>
+      <c r="L125">
+        <v>-69.923349000000002</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A126" t="s">
+        <v>433</v>
+      </c>
+      <c r="B126" s="8">
+        <v>46014</v>
+      </c>
+      <c r="C126" s="8">
+        <v>46014</v>
+      </c>
+      <c r="D126" t="s">
+        <v>294</v>
+      </c>
+      <c r="E126" t="s">
+        <v>391</v>
+      </c>
+      <c r="F126" t="s">
+        <v>392</v>
+      </c>
+      <c r="G126" t="s">
+        <v>58</v>
+      </c>
+      <c r="H126" t="s">
+        <v>28</v>
+      </c>
+      <c r="I126" t="s">
+        <v>434</v>
+      </c>
+      <c r="J126" t="s">
+        <v>22</v>
+      </c>
+      <c r="K126">
+        <v>-11.025029999999999</v>
+      </c>
+      <c r="L126">
+        <v>-74.868764999999996</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A127" t="s">
+        <v>435</v>
+      </c>
+      <c r="B127" s="8">
+        <v>46014</v>
+      </c>
+      <c r="C127" s="8">
+        <v>46013</v>
+      </c>
+      <c r="D127" t="s">
+        <v>436</v>
+      </c>
+      <c r="E127" t="s">
+        <v>437</v>
+      </c>
+      <c r="F127" t="s">
+        <v>438</v>
+      </c>
+      <c r="G127" t="s">
+        <v>355</v>
+      </c>
+      <c r="H127" t="s">
+        <v>28</v>
+      </c>
+      <c r="I127" t="s">
+        <v>439</v>
+      </c>
+      <c r="J127" t="s">
+        <v>22</v>
+      </c>
+      <c r="K127">
+        <v>-14.928466</v>
+      </c>
+      <c r="L127">
+        <v>-74.828006000000002</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A128" t="s">
+        <v>440</v>
+      </c>
+      <c r="B128" s="8">
+        <v>46015</v>
+      </c>
+      <c r="C128" s="8">
+        <v>46015</v>
+      </c>
+      <c r="D128" t="s">
+        <v>24</v>
+      </c>
+      <c r="E128" t="s">
+        <v>441</v>
+      </c>
+      <c r="F128" t="s">
+        <v>442</v>
+      </c>
+      <c r="G128" t="s">
+        <v>58</v>
+      </c>
+      <c r="H128" t="s">
+        <v>330</v>
+      </c>
+      <c r="I128" t="s">
+        <v>443</v>
+      </c>
+      <c r="J128" t="s">
+        <v>444</v>
+      </c>
+      <c r="K128">
+        <v>-12.795697000000001</v>
+      </c>
+      <c r="L128">
+        <v>-72.105086</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A129" t="s">
+        <v>445</v>
+      </c>
+      <c r="B129" s="8">
+        <v>46015</v>
+      </c>
+      <c r="C129" s="8">
+        <v>46014</v>
+      </c>
+      <c r="D129" t="s">
+        <v>137</v>
+      </c>
+      <c r="E129" t="s">
+        <v>148</v>
+      </c>
+      <c r="F129" t="s">
+        <v>446</v>
+      </c>
+      <c r="G129" t="s">
+        <v>58</v>
+      </c>
+      <c r="H129" t="s">
+        <v>20</v>
+      </c>
+      <c r="I129" t="s">
+        <v>447</v>
+      </c>
+      <c r="J129" t="s">
+        <v>22</v>
+      </c>
+      <c r="K129">
+        <v>-6.3457840000000001</v>
+      </c>
+      <c r="L129">
+        <v>-78.163993000000005</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A130" t="s">
+        <v>448</v>
+      </c>
+      <c r="B130" s="8">
+        <v>46015</v>
+      </c>
+      <c r="C130" s="8">
+        <v>46014</v>
+      </c>
+      <c r="D130" t="s">
+        <v>133</v>
+      </c>
+      <c r="E130" t="s">
+        <v>449</v>
+      </c>
+      <c r="F130" t="s">
+        <v>450</v>
+      </c>
+      <c r="G130" t="s">
+        <v>38</v>
+      </c>
+      <c r="H130" t="s">
+        <v>20</v>
+      </c>
+      <c r="I130" t="s">
+        <v>451</v>
+      </c>
+      <c r="J130" t="s">
+        <v>22</v>
+      </c>
+      <c r="K130">
+        <v>-9.1487069999999999</v>
+      </c>
+      <c r="L130">
+        <v>-77.818721999999994</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A131" t="s">
+        <v>452</v>
+      </c>
+      <c r="B131" s="8">
+        <v>46016</v>
+      </c>
+      <c r="C131" s="8">
+        <v>46016</v>
+      </c>
+      <c r="D131" t="s">
+        <v>68</v>
+      </c>
+      <c r="E131" t="s">
+        <v>68</v>
+      </c>
+      <c r="F131" t="s">
+        <v>453</v>
+      </c>
+      <c r="G131" t="s">
+        <v>355</v>
+      </c>
+      <c r="H131" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="I131" t="s">
+        <v>454</v>
+      </c>
+      <c r="J131" t="s">
+        <v>455</v>
+      </c>
+      <c r="K131">
+        <v>-12.033052</v>
+      </c>
+      <c r="L131">
+        <v>-77.03304</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A132" t="s">
+        <v>456</v>
+      </c>
+      <c r="B132" s="8">
+        <v>46018</v>
+      </c>
+      <c r="C132" s="8">
+        <v>46018</v>
+      </c>
+      <c r="D132" t="s">
+        <v>458</v>
+      </c>
+      <c r="E132" t="s">
+        <v>459</v>
+      </c>
+      <c r="F132" t="s">
+        <v>460</v>
+      </c>
+      <c r="G132" t="s">
+        <v>207</v>
+      </c>
+      <c r="H132" t="s">
+        <v>20</v>
+      </c>
+      <c r="I132" t="s">
+        <v>457</v>
+      </c>
+      <c r="J132" t="s">
+        <v>30</v>
+      </c>
+      <c r="K132">
+        <v>-8.8775969999999997</v>
+      </c>
+      <c r="L132">
+        <v>-78.401116000000002</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A133" t="s">
+        <v>461</v>
+      </c>
+      <c r="B133" s="8">
+        <v>46018</v>
+      </c>
+      <c r="C133" s="8">
+        <v>46018</v>
+      </c>
+      <c r="D133" t="s">
+        <v>429</v>
+      </c>
+      <c r="E133" t="s">
+        <v>462</v>
+      </c>
+      <c r="F133" t="s">
+        <v>429</v>
+      </c>
+      <c r="G133" t="s">
+        <v>19</v>
+      </c>
+      <c r="H133" t="s">
+        <v>20</v>
+      </c>
+      <c r="I133" t="s">
+        <v>457</v>
+      </c>
+      <c r="J133" t="s">
+        <v>20</v>
+      </c>
+      <c r="K133">
+        <v>-12.629542000000001</v>
+      </c>
+      <c r="L133">
+        <v>-70.675352000000004</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="135" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="136" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="137" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="138" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="139" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="140" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="141" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="142" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="143" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="144" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="145" ht="15.75" customHeight="1"/>
     <row r="146" ht="15.75" customHeight="1"/>
     <row r="147" ht="15.75" customHeight="1"/>
@@ -8240,6 +8761,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <autoFilter ref="A1:L123" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -8441,7 +8963,7 @@
         <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -8529,7 +9051,7 @@
         <v>198</v>
       </c>
       <c r="B16" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F16">
         <v>4</v>
@@ -8767,7 +9289,7 @@
         <v>289</v>
       </c>
       <c r="B30" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -8781,7 +9303,7 @@
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B31" t="s">
         <v>324</v>
@@ -8801,31 +9323,73 @@
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B32" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="33" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A33" t="s">
+        <v>423</v>
+      </c>
+      <c r="B33" t="s">
+        <v>324</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>46013</v>
+      </c>
+      <c r="H33">
+        <v>46011</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A34" t="s">
+        <v>423</v>
+      </c>
+      <c r="B34" t="s">
+        <v>324</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A35" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C35" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>

--- a/emergencias.xlsx
+++ b/emergencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whuatay\Documents\TDOCUMENTOS\2025\COE MIDIS\Aplicativo_web\6. COE_TABLERO_SEMANAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194BB16C-8140-48B9-8CB1-041743A571F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3658375C-055E-4005-8B72-2C3C2F6EFD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="463">
   <si>
     <t>fecha</t>
   </si>
@@ -9377,7 +9377,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A36" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="B36" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="12">
+        <v>14</v>
+      </c>
+    </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="38" spans="1:8" ht="15.75" customHeight="1"/>
     <row r="39" spans="1:8" ht="15.75" customHeight="1"/>

--- a/emergencias.xlsx
+++ b/emergencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whuatay\Documents\TDOCUMENTOS\2025\COE MIDIS\Aplicativo_web\6. COE_TABLERO_SEMANAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3658375C-055E-4005-8B72-2C3C2F6EFD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0382E8B5-64F6-4A78-A53A-9F28117A5BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meta" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="498">
   <si>
     <t>fecha</t>
   </si>
@@ -1430,6 +1430,111 @@
   </si>
   <si>
     <t>Manu</t>
+  </si>
+  <si>
+    <t>EV_2025_133</t>
+  </si>
+  <si>
+    <t>Daños materiales (viviendas) en la localidad de Pucacaca</t>
+  </si>
+  <si>
+    <t>EV_2025_134</t>
+  </si>
+  <si>
+    <t>Fitzcarrald</t>
+  </si>
+  <si>
+    <t>Daños materiales (viviendas) en el CP Isla de los Valles</t>
+  </si>
+  <si>
+    <t>EV_2025_135</t>
+  </si>
+  <si>
+    <t>Pozuzo</t>
+  </si>
+  <si>
+    <t>Daños en vía de transporte (tramo Pozuzo-Oxapampa) en el sector Huampal</t>
+  </si>
+  <si>
+    <t>EV_2025_136</t>
+  </si>
+  <si>
+    <t>San Juan de Lurigancho</t>
+  </si>
+  <si>
+    <t>Daños a infraestructura en la Av. Los Eucaliptos N° 228</t>
+  </si>
+  <si>
+    <t>EV_2025_137</t>
+  </si>
+  <si>
+    <t>Huamanga</t>
+  </si>
+  <si>
+    <t>Chiara</t>
+  </si>
+  <si>
+    <t>Daños a la cobertura natural y 01 herido en la comunidad de Secchapampa</t>
+  </si>
+  <si>
+    <t>PN PAIS: La UT realiza el seguimiento correspondiente</t>
+  </si>
+  <si>
+    <t>EV_2025_138</t>
+  </si>
+  <si>
+    <t>Tocache</t>
+  </si>
+  <si>
+    <t>Nuevo Progreso</t>
+  </si>
+  <si>
+    <t>Daños materiales (viviendas, infraestructura educativa e infraestructura de transporte, servicios básicos) y a cultivos en la localidad de Nuevo Progreso</t>
+  </si>
+  <si>
+    <t>EV_2025_139</t>
+  </si>
+  <si>
+    <t>Urubamba</t>
+  </si>
+  <si>
+    <t>Machupicchu</t>
+  </si>
+  <si>
+    <t>Daños a la vida y salud de pasajeros tras el choque de dos trenes en ruta al distrito de Machupicchu (Aguas Calientes)</t>
+  </si>
+  <si>
+    <t>MINSA: movilización de ambulancias</t>
+  </si>
+  <si>
+    <t>EV_2025_140</t>
+  </si>
+  <si>
+    <t>Daños materiales (viviendas) en el A.H. 15 de noviembre</t>
+  </si>
+  <si>
+    <t>EV_2025_141</t>
+  </si>
+  <si>
+    <t>Echarate</t>
+  </si>
+  <si>
+    <t>Daños a vía de transporte (Quillabamba - Echarate) en el sector Pacpachayoc . Vía bloqueada</t>
+  </si>
+  <si>
+    <t>MTC: limpieza con maquinaria</t>
+  </si>
+  <si>
+    <t>EV_2025_142</t>
+  </si>
+  <si>
+    <t>Cangallo</t>
+  </si>
+  <si>
+    <t>Daños a la cobertura natural en el sector Lambras Pampa</t>
+  </si>
+  <si>
+    <t>Población: control y extinción del incendio</t>
   </si>
 </sst>
 </file>
@@ -7893,16 +7998,386 @@
         <v>-70.675352000000004</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="135" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="136" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="137" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="138" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="139" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="140" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="141" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="142" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="143" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="134" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A134" t="s">
+        <v>463</v>
+      </c>
+      <c r="B134">
+        <v>46020</v>
+      </c>
+      <c r="C134">
+        <v>46019</v>
+      </c>
+      <c r="D134" t="s">
+        <v>56</v>
+      </c>
+      <c r="E134" t="s">
+        <v>74</v>
+      </c>
+      <c r="F134" t="s">
+        <v>75</v>
+      </c>
+      <c r="G134" t="s">
+        <v>51</v>
+      </c>
+      <c r="H134" t="s">
+        <v>20</v>
+      </c>
+      <c r="I134" t="s">
+        <v>464</v>
+      </c>
+      <c r="J134" t="s">
+        <v>22</v>
+      </c>
+      <c r="K134">
+        <v>-6.8402329999999996</v>
+      </c>
+      <c r="L134">
+        <v>-76.363045999999997</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A135" t="s">
+        <v>465</v>
+      </c>
+      <c r="B135">
+        <v>46020</v>
+      </c>
+      <c r="C135">
+        <v>46020</v>
+      </c>
+      <c r="D135" t="s">
+        <v>429</v>
+      </c>
+      <c r="E135" t="s">
+        <v>462</v>
+      </c>
+      <c r="F135" t="s">
+        <v>466</v>
+      </c>
+      <c r="G135" t="s">
+        <v>19</v>
+      </c>
+      <c r="H135" t="s">
+        <v>330</v>
+      </c>
+      <c r="I135" t="s">
+        <v>467</v>
+      </c>
+      <c r="J135" t="s">
+        <v>22</v>
+      </c>
+      <c r="K135">
+        <v>-11.850403999999999</v>
+      </c>
+      <c r="L135">
+        <v>-71.634663000000003</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A136" t="s">
+        <v>468</v>
+      </c>
+      <c r="B136">
+        <v>46020</v>
+      </c>
+      <c r="C136">
+        <v>46019</v>
+      </c>
+      <c r="D136" t="s">
+        <v>44</v>
+      </c>
+      <c r="E136" t="s">
+        <v>365</v>
+      </c>
+      <c r="F136" t="s">
+        <v>469</v>
+      </c>
+      <c r="G136" t="s">
+        <v>272</v>
+      </c>
+      <c r="H136" t="s">
+        <v>20</v>
+      </c>
+      <c r="I136" t="s">
+        <v>470</v>
+      </c>
+      <c r="J136" t="s">
+        <v>22</v>
+      </c>
+      <c r="K136">
+        <v>-10.132719</v>
+      </c>
+      <c r="L136">
+        <v>-75.586271999999994</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A137" t="s">
+        <v>471</v>
+      </c>
+      <c r="B137">
+        <v>46020</v>
+      </c>
+      <c r="C137">
+        <v>46020</v>
+      </c>
+      <c r="D137" t="s">
+        <v>68</v>
+      </c>
+      <c r="E137" t="s">
+        <v>68</v>
+      </c>
+      <c r="F137" t="s">
+        <v>472</v>
+      </c>
+      <c r="G137" t="s">
+        <v>355</v>
+      </c>
+      <c r="H137" t="s">
+        <v>330</v>
+      </c>
+      <c r="I137" t="s">
+        <v>473</v>
+      </c>
+      <c r="J137" t="s">
+        <v>22</v>
+      </c>
+      <c r="K137">
+        <v>-11.945947</v>
+      </c>
+      <c r="L137">
+        <v>-76.971463999999997</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A138" t="s">
+        <v>474</v>
+      </c>
+      <c r="B138">
+        <v>46020</v>
+      </c>
+      <c r="C138">
+        <v>46019</v>
+      </c>
+      <c r="D138" t="s">
+        <v>84</v>
+      </c>
+      <c r="E138" t="s">
+        <v>475</v>
+      </c>
+      <c r="F138" t="s">
+        <v>476</v>
+      </c>
+      <c r="G138" t="s">
+        <v>38</v>
+      </c>
+      <c r="H138" t="s">
+        <v>20</v>
+      </c>
+      <c r="I138" t="s">
+        <v>477</v>
+      </c>
+      <c r="J138" t="s">
+        <v>478</v>
+      </c>
+      <c r="K138">
+        <v>-13.375748</v>
+      </c>
+      <c r="L138">
+        <v>-74.158625999999998</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A139" t="s">
+        <v>479</v>
+      </c>
+      <c r="B139">
+        <v>46020</v>
+      </c>
+      <c r="C139">
+        <v>46016</v>
+      </c>
+      <c r="D139" t="s">
+        <v>56</v>
+      </c>
+      <c r="E139" t="s">
+        <v>480</v>
+      </c>
+      <c r="F139" t="s">
+        <v>481</v>
+      </c>
+      <c r="G139" t="s">
+        <v>58</v>
+      </c>
+      <c r="H139" t="s">
+        <v>20</v>
+      </c>
+      <c r="I139" t="s">
+        <v>482</v>
+      </c>
+      <c r="J139" t="s">
+        <v>22</v>
+      </c>
+      <c r="K139">
+        <v>-8.5256430000000005</v>
+      </c>
+      <c r="L139">
+        <v>-76.212536</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A140" t="s">
+        <v>483</v>
+      </c>
+      <c r="B140">
+        <v>46021</v>
+      </c>
+      <c r="C140">
+        <v>46021</v>
+      </c>
+      <c r="D140" t="s">
+        <v>24</v>
+      </c>
+      <c r="E140" t="s">
+        <v>484</v>
+      </c>
+      <c r="F140" t="s">
+        <v>485</v>
+      </c>
+      <c r="G140" t="s">
+        <v>317</v>
+      </c>
+      <c r="H140" t="s">
+        <v>330</v>
+      </c>
+      <c r="I140" t="s">
+        <v>486</v>
+      </c>
+      <c r="J140" t="s">
+        <v>487</v>
+      </c>
+      <c r="K140">
+        <v>-13.201471</v>
+      </c>
+      <c r="L140">
+        <v>-72.500158999999996</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A141" t="s">
+        <v>488</v>
+      </c>
+      <c r="B141">
+        <v>46021</v>
+      </c>
+      <c r="C141">
+        <v>46021</v>
+      </c>
+      <c r="D141" t="s">
+        <v>48</v>
+      </c>
+      <c r="E141" t="s">
+        <v>49</v>
+      </c>
+      <c r="F141" t="s">
+        <v>422</v>
+      </c>
+      <c r="G141" t="s">
+        <v>94</v>
+      </c>
+      <c r="H141" t="s">
+        <v>330</v>
+      </c>
+      <c r="I141" t="s">
+        <v>489</v>
+      </c>
+      <c r="J141" t="s">
+        <v>22</v>
+      </c>
+      <c r="K141">
+        <v>-3.811598</v>
+      </c>
+      <c r="L141">
+        <v>-73.211978000000002</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A142" t="s">
+        <v>490</v>
+      </c>
+      <c r="B142">
+        <v>46021</v>
+      </c>
+      <c r="C142">
+        <v>46021</v>
+      </c>
+      <c r="D142" t="s">
+        <v>24</v>
+      </c>
+      <c r="E142" t="s">
+        <v>25</v>
+      </c>
+      <c r="F142" t="s">
+        <v>491</v>
+      </c>
+      <c r="G142" t="s">
+        <v>167</v>
+      </c>
+      <c r="H142" t="s">
+        <v>330</v>
+      </c>
+      <c r="I142" t="s">
+        <v>492</v>
+      </c>
+      <c r="J142" t="s">
+        <v>493</v>
+      </c>
+      <c r="K142">
+        <v>-12.355022</v>
+      </c>
+      <c r="L142">
+        <v>-72.832802999999998</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A143" t="s">
+        <v>494</v>
+      </c>
+      <c r="B143">
+        <v>46021</v>
+      </c>
+      <c r="C143">
+        <v>46020</v>
+      </c>
+      <c r="D143" t="s">
+        <v>84</v>
+      </c>
+      <c r="E143" t="s">
+        <v>495</v>
+      </c>
+      <c r="F143" t="s">
+        <v>495</v>
+      </c>
+      <c r="G143" t="s">
+        <v>341</v>
+      </c>
+      <c r="H143" t="s">
+        <v>20</v>
+      </c>
+      <c r="I143" t="s">
+        <v>496</v>
+      </c>
+      <c r="J143" t="s">
+        <v>497</v>
+      </c>
+      <c r="K143">
+        <v>-13.599735000000001</v>
+      </c>
+      <c r="L143">
+        <v>-74.110073</v>
+      </c>
+    </row>
     <row r="144" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="145" ht="15.75" customHeight="1"/>
     <row r="146" ht="15.75" customHeight="1"/>
@@ -10356,6 +10831,6 @@
     <sortCondition ref="A2:A30"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>